--- a/data/ern2026/questionari.xlsx
+++ b/data/ern2026/questionari.xlsx
@@ -164,8 +164,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DatiHEPscape" displayName="DatiHEPscape" ref="A6:N213" headerRowCount="1">
-  <autoFilter ref="A6:N213"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DatiHEPscape" displayName="DatiHEPscape" ref="A6:N236" headerRowCount="1">
+  <autoFilter ref="A6:N236"/>
   <tableColumns count="14">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Q1"/>
@@ -187,8 +187,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="OriginaliHEPscape" displayName="OriginaliHEPscape" ref="A1:R208" headerRowCount="1">
-  <autoFilter ref="A1:R208"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="OriginaliHEPscape" displayName="OriginaliHEPscape" ref="A1:R231" headerRowCount="1">
+  <autoFilter ref="A1:R231"/>
   <tableColumns count="18">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Q1"/>
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N213"/>
+  <dimension ref="A1:N236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HEPscape! | Evento ERNEST - ERN 2026 | 207 questionari</t>
+          <t>HEPscape! | Evento ERNEST - ERN 2026 | 230 questionari</t>
         </is>
       </c>
     </row>
@@ -11451,44 +11451,1216 @@
         </is>
       </c>
     </row>
+    <row r="214" ht="34" customHeight="1">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-001</t>
+        </is>
+      </c>
+      <c r="B214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" s="1" t="inlineStr">
+        <is>
+          <t>SIMPATICA</t>
+        </is>
+      </c>
+      <c r="D214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="L214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N214" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="34" customHeight="1">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-002</t>
+        </is>
+      </c>
+      <c r="B215" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D215" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F215" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N215" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="34" customHeight="1">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-003</t>
+        </is>
+      </c>
+      <c r="B216" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C216" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D216" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N216" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="34" customHeight="1">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-004</t>
+        </is>
+      </c>
+      <c r="B217" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C217" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D217" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="H217" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="I217" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K217" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N217" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="34" customHeight="1">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-005</t>
+        </is>
+      </c>
+      <c r="B218" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C218" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D218" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I218" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M218" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N218" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="34" customHeight="1">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-006</t>
+        </is>
+      </c>
+      <c r="B219" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C219" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D219" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M219" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N219" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="34" customHeight="1">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-007</t>
+        </is>
+      </c>
+      <c r="B220" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C220" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D220" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I220" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J220" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K220" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L220" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N220" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="34" customHeight="1">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-008</t>
+        </is>
+      </c>
+      <c r="B221" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D221" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F221" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G221" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I221" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K221" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L221" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N221" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="34" customHeight="1">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-009</t>
+        </is>
+      </c>
+      <c r="B222" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" s="1" t="inlineStr">
+        <is>
+          <t>MI SONO DIVERTITO</t>
+        </is>
+      </c>
+      <c r="D222" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I222" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K222" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L222" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N222" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="34" customHeight="1">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-010</t>
+        </is>
+      </c>
+      <c r="B223" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C223" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D223" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I223" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K223" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N223" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="34" customHeight="1">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-011</t>
+        </is>
+      </c>
+      <c r="B224" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" s="1" t="inlineStr">
+        <is>
+          <t>INGRESSI BELLO?</t>
+        </is>
+      </c>
+      <c r="D224" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I224" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K224" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M224" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N224" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="34" customHeight="1">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-012</t>
+        </is>
+      </c>
+      <c r="B225" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C225" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D225" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I225" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K225" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M225" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N225" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="34" customHeight="1">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-013</t>
+        </is>
+      </c>
+      <c r="B226" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C226" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D226" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I226" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K226" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M226" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N226" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="34" customHeight="1">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-014</t>
+        </is>
+      </c>
+      <c r="B227" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C227" s="1" t="inlineStr">
+        <is>
+          <t>MOLTO BELLA</t>
+        </is>
+      </c>
+      <c r="D227" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F227" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I227" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J227" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K227" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M227" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N227" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="34" customHeight="1">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-015</t>
+        </is>
+      </c>
+      <c r="B228" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C228" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D228" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E228" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F228" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H228" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I228" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M228" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N228" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="34" customHeight="1">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-016</t>
+        </is>
+      </c>
+      <c r="B229" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C229" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D229" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E229" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F229" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H229" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J229" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M229" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N229" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="36" customHeight="1">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-017</t>
+        </is>
+      </c>
+      <c r="B230" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C230" s="1" t="inlineStr">
+        <is>
+          <t>MI E' PIACIUTA TANTISSIMO BELLISSIMA ESPERIENZA</t>
+        </is>
+      </c>
+      <c r="D230" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I230" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N230" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="34" customHeight="1">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-018</t>
+        </is>
+      </c>
+      <c r="B231" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C231" s="1" t="inlineStr">
+        <is>
+          <t>CARINA E BEN ORGANIZZATA</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E231" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I231" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J231" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L231" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N231" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="34" customHeight="1">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-019</t>
+        </is>
+      </c>
+      <c r="B232" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C232" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D232" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F232" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G232" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I232" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K232" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M232" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N232" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="34" customHeight="1">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-020</t>
+        </is>
+      </c>
+      <c r="B233" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C233" s="1" t="inlineStr">
+        <is>
+          <t>CARINA E BEN ORGANIZZATA</t>
+        </is>
+      </c>
+      <c r="D233" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I233" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J233" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L233" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N233" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="34" customHeight="1">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-021</t>
+        </is>
+      </c>
+      <c r="B234" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C234" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE SCIENTIFICO</t>
+        </is>
+      </c>
+      <c r="D234" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F234" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G234" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I234" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K234" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L234" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M234" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N234" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="34" customHeight="1">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-022</t>
+        </is>
+      </c>
+      <c r="B235" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C235" s="1" t="inlineStr">
+        <is>
+          <t>BUFFA</t>
+        </is>
+      </c>
+      <c r="D235" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F235" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G235" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I235" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J235" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K235" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M235" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N235" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="34" customHeight="1">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-023</t>
+        </is>
+      </c>
+      <c r="B236" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C236" s="1" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="D236" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F236" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="H236" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="I236" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K236" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M236" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="N236" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B7:L213">
+  <conditionalFormatting sqref="B7:L236">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>999</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="10">
-    <dataValidation sqref="B7:B213" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="B7:B236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:D213" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="D7:D236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="E7:E213" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="E7:E236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="F7:F213" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="F7:F236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="G7:G213" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="G7:G236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="H7:H213" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="H7:H236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="I7:I213" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="I7:I236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="J7:J213" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="J7:J236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,3,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="K7:K213" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="K7:K236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,3,4,5,6,7,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="L7:L213" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="L7:L236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,999"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11505,7 +12677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R208"/>
+  <dimension ref="A1:R231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -28730,6 +29902,1965 @@
       </c>
       <c r="R208" s="1" t="inlineStr"/>
     </row>
+    <row r="209" ht="52" customHeight="1">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-001</t>
+        </is>
+      </c>
+      <c r="B209" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C209" s="1" t="inlineStr">
+        <is>
+          <t>Simpatica</t>
+        </is>
+      </c>
+      <c r="D209" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E209" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F209" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G209" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H209" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I209" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J209" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K209" s="1" t="inlineStr"/>
+      <c r="L209" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M209" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N209" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=1</t>
+        </is>
+      </c>
+      <c r="O209" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P209" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q209" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R209" s="1" t="inlineStr"/>
+    </row>
+    <row r="210" ht="52" customHeight="1">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-002</t>
+        </is>
+      </c>
+      <c r="B210" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C210" s="1" t="inlineStr"/>
+      <c r="D210" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E210" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F210" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G210" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H210" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I210" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J210" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K210" s="1" t="inlineStr">
+        <is>
+          <t>11-14</t>
+        </is>
+      </c>
+      <c r="L210" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M210" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N210" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=2</t>
+        </is>
+      </c>
+      <c r="O210" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P210" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q210" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R210" s="1" t="inlineStr"/>
+    </row>
+    <row r="211" ht="52" customHeight="1">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-003</t>
+        </is>
+      </c>
+      <c r="B211" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C211" s="1" t="inlineStr"/>
+      <c r="D211" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E211" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F211" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G211" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H211" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I211" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J211" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K211" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L211" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M211" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N211" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=3</t>
+        </is>
+      </c>
+      <c r="O211" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P211" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q211" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R211" s="1" t="inlineStr"/>
+    </row>
+    <row r="212" ht="52" customHeight="1">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-004</t>
+        </is>
+      </c>
+      <c r="B212" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C212" s="1" t="inlineStr"/>
+      <c r="D212" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E212" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F212" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G212" s="1" t="inlineStr"/>
+      <c r="H212" s="1" t="inlineStr"/>
+      <c r="I212" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J212" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K212" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L212" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M212" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N212" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=4</t>
+        </is>
+      </c>
+      <c r="O212" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P212" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q212" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R212" s="1" t="inlineStr"/>
+    </row>
+    <row r="213" ht="52" customHeight="1">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-005</t>
+        </is>
+      </c>
+      <c r="B213" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C213" s="1" t="inlineStr"/>
+      <c r="D213" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E213" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F213" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G213" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H213" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I213" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J213" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K213" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L213" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M213" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N213" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=5</t>
+        </is>
+      </c>
+      <c r="O213" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P213" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q213" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R213" s="1" t="inlineStr"/>
+    </row>
+    <row r="214" ht="52" customHeight="1">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-006</t>
+        </is>
+      </c>
+      <c r="B214" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C214" s="1" t="inlineStr"/>
+      <c r="D214" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E214" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F214" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G214" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H214" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I214" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J214" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K214" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L214" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M214" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N214" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=6</t>
+        </is>
+      </c>
+      <c r="O214" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P214" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q214" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R214" s="1" t="inlineStr"/>
+    </row>
+    <row r="215" ht="52" customHeight="1">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-007</t>
+        </is>
+      </c>
+      <c r="B215" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C215" s="1" t="inlineStr"/>
+      <c r="D215" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E215" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F215" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G215" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H215" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I215" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J215" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K215" s="1" t="inlineStr">
+        <is>
+          <t>11-14</t>
+        </is>
+      </c>
+      <c r="L215" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M215" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N215" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=7</t>
+        </is>
+      </c>
+      <c r="O215" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P215" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q215" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R215" s="1" t="inlineStr"/>
+    </row>
+    <row r="216" ht="52" customHeight="1">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-008</t>
+        </is>
+      </c>
+      <c r="B216" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C216" s="1" t="inlineStr"/>
+      <c r="D216" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E216" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F216" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G216" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H216" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I216" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J216" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K216" s="1" t="inlineStr">
+        <is>
+          <t>11-14</t>
+        </is>
+      </c>
+      <c r="L216" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M216" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N216" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=8</t>
+        </is>
+      </c>
+      <c r="O216" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P216" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q216" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R216" s="1" t="inlineStr"/>
+    </row>
+    <row r="217" ht="52" customHeight="1">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-009</t>
+        </is>
+      </c>
+      <c r="B217" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C217" s="1" t="inlineStr">
+        <is>
+          <t>mi sono divertito</t>
+        </is>
+      </c>
+      <c r="D217" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E217" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F217" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G217" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H217" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I217" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J217" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K217" s="1" t="inlineStr">
+        <is>
+          <t>11-14</t>
+        </is>
+      </c>
+      <c r="L217" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M217" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N217" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=9</t>
+        </is>
+      </c>
+      <c r="O217" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P217" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q217" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R217" s="1" t="inlineStr"/>
+    </row>
+    <row r="218" ht="52" customHeight="1">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-010</t>
+        </is>
+      </c>
+      <c r="B218" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C218" s="1" t="inlineStr"/>
+      <c r="D218" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E218" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F218" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G218" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H218" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I218" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J218" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K218" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L218" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M218" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N218" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=10</t>
+        </is>
+      </c>
+      <c r="O218" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P218" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q218" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R218" s="1" t="inlineStr"/>
+    </row>
+    <row r="219" ht="84" customHeight="1">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-011</t>
+        </is>
+      </c>
+      <c r="B219" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="inlineStr">
+        <is>
+          <t>ingressi bello?</t>
+        </is>
+      </c>
+      <c r="D219" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E219" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F219" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G219" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H219" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I219" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J219" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K219" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L219" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M219" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.
+Q2: Trascrizione fornita dall’utente: punto interrogativo conservato; nessuna verifica su fotografia.</t>
+        </is>
+      </c>
+      <c r="N219" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=11</t>
+        </is>
+      </c>
+      <c r="O219" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P219" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q219" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R219" s="1" t="inlineStr"/>
+    </row>
+    <row r="220" ht="52" customHeight="1">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-012</t>
+        </is>
+      </c>
+      <c r="B220" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="inlineStr"/>
+      <c r="D220" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E220" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F220" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G220" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H220" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I220" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J220" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K220" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L220" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M220" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N220" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=12</t>
+        </is>
+      </c>
+      <c r="O220" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P220" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q220" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R220" s="1" t="inlineStr"/>
+    </row>
+    <row r="221" ht="52" customHeight="1">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-013</t>
+        </is>
+      </c>
+      <c r="B221" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C221" s="1" t="inlineStr"/>
+      <c r="D221" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E221" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F221" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G221" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H221" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I221" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J221" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K221" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L221" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M221" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N221" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=13</t>
+        </is>
+      </c>
+      <c r="O221" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P221" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q221" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R221" s="1" t="inlineStr"/>
+    </row>
+    <row r="222" ht="52" customHeight="1">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-014</t>
+        </is>
+      </c>
+      <c r="B222" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="inlineStr">
+        <is>
+          <t>molto bella</t>
+        </is>
+      </c>
+      <c r="D222" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E222" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F222" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G222" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H222" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I222" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J222" s="1" t="inlineStr">
+        <is>
+          <t>non risp</t>
+        </is>
+      </c>
+      <c r="K222" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L222" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M222" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N222" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=14</t>
+        </is>
+      </c>
+      <c r="O222" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P222" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q222" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R222" s="1" t="inlineStr"/>
+    </row>
+    <row r="223" ht="52" customHeight="1">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-015</t>
+        </is>
+      </c>
+      <c r="B223" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C223" s="1" t="inlineStr">
+        <is>
+          <t>interessante</t>
+        </is>
+      </c>
+      <c r="D223" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E223" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F223" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G223" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H223" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I223" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J223" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K223" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L223" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M223" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N223" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=15</t>
+        </is>
+      </c>
+      <c r="O223" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P223" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q223" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R223" s="1" t="inlineStr"/>
+    </row>
+    <row r="224" ht="52" customHeight="1">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-016</t>
+        </is>
+      </c>
+      <c r="B224" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C224" s="1" t="inlineStr"/>
+      <c r="D224" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E224" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F224" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G224" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H224" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I224" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J224" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K224" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L224" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M224" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N224" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=16</t>
+        </is>
+      </c>
+      <c r="O224" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P224" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q224" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R224" s="1" t="inlineStr"/>
+    </row>
+    <row r="225" ht="52" customHeight="1">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-017</t>
+        </is>
+      </c>
+      <c r="B225" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="inlineStr">
+        <is>
+          <t>mi e' piaciuta tantissimo bellissima esperienza</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E225" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F225" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G225" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H225" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I225" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J225" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K225" s="1" t="inlineStr">
+        <is>
+          <t>11-14</t>
+        </is>
+      </c>
+      <c r="L225" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M225" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N225" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=17</t>
+        </is>
+      </c>
+      <c r="O225" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P225" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q225" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R225" s="1" t="inlineStr"/>
+    </row>
+    <row r="226" ht="84" customHeight="1">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-018</t>
+        </is>
+      </c>
+      <c r="B226" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C226" s="1" t="inlineStr">
+        <is>
+          <t>carina e ben organizzata</t>
+        </is>
+      </c>
+      <c r="D226" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E226" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F226" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G226" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H226" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I226" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J226" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K226" s="1" t="inlineStr">
+        <is>
+          <t>19-25</t>
+        </is>
+      </c>
+      <c r="L226" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M226" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.
+riga: Le righe 18 e 20 della tabella sono identiche; mantenute come due schede distinte.</t>
+        </is>
+      </c>
+      <c r="N226" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=18</t>
+        </is>
+      </c>
+      <c r="O226" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P226" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q226" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R226" s="1" t="inlineStr"/>
+    </row>
+    <row r="227" ht="52" customHeight="1">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-019</t>
+        </is>
+      </c>
+      <c r="B227" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C227" s="1" t="inlineStr"/>
+      <c r="D227" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E227" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F227" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G227" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H227" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I227" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J227" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K227" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L227" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M227" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N227" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=19</t>
+        </is>
+      </c>
+      <c r="O227" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P227" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q227" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R227" s="1" t="inlineStr"/>
+    </row>
+    <row r="228" ht="84" customHeight="1">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-020</t>
+        </is>
+      </c>
+      <c r="B228" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C228" s="1" t="inlineStr">
+        <is>
+          <t>carina e ben organizzata</t>
+        </is>
+      </c>
+      <c r="D228" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E228" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F228" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G228" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H228" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I228" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J228" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="K228" s="1" t="inlineStr">
+        <is>
+          <t>19-25</t>
+        </is>
+      </c>
+      <c r="L228" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M228" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.
+riga: Le righe 18 e 20 della tabella sono identiche; mantenute come due schede distinte.</t>
+        </is>
+      </c>
+      <c r="N228" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=20</t>
+        </is>
+      </c>
+      <c r="O228" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P228" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q228" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R228" s="1" t="inlineStr"/>
+    </row>
+    <row r="229" ht="52" customHeight="1">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-021</t>
+        </is>
+      </c>
+      <c r="B229" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C229" s="1" t="inlineStr">
+        <is>
+          <t>interessante scientifico</t>
+        </is>
+      </c>
+      <c r="D229" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E229" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F229" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G229" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H229" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I229" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J229" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K229" s="1" t="inlineStr">
+        <is>
+          <t>11-14</t>
+        </is>
+      </c>
+      <c r="L229" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M229" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N229" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=21</t>
+        </is>
+      </c>
+      <c r="O229" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P229" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q229" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R229" s="1" t="inlineStr"/>
+    </row>
+    <row r="230" ht="52" customHeight="1">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-022</t>
+        </is>
+      </c>
+      <c r="B230" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C230" s="1" t="inlineStr">
+        <is>
+          <t>buffa</t>
+        </is>
+      </c>
+      <c r="D230" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E230" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F230" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G230" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H230" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I230" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J230" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K230" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L230" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M230" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N230" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=22</t>
+        </is>
+      </c>
+      <c r="O230" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P230" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q230" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R230" s="1" t="inlineStr"/>
+    </row>
+    <row r="231" ht="52" customHeight="1">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>PISA-ERN2026-023</t>
+        </is>
+      </c>
+      <c r="B231" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C231" s="1" t="inlineStr">
+        <is>
+          <t>bello</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E231" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F231" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G231" s="1" t="inlineStr"/>
+      <c r="H231" s="1" t="inlineStr"/>
+      <c r="I231" s="1" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J231" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K231" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L231" s="1" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="M231" s="1" t="inlineStr">
+        <is>
+          <t>codifica: Valori originali numerici Q1/Q3–Q7 nella scala Pisa: 2→0, 1→1, 0→2. Sì→1, No→0. Celle vuote→999 in Excel.</t>
+        </is>
+      </c>
+      <c r="N231" s="1" t="inlineStr">
+        <is>
+          <t>pisa_tabella_originale.csv#N=23</t>
+        </is>
+      </c>
+      <c r="O231" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="P231" s="1" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="Q231" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R231" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/ern2026/questionari.xlsx
+++ b/data/ern2026/questionari.xlsx
@@ -164,8 +164,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DatiHEPscape" displayName="DatiHEPscape" ref="A6:N236" headerRowCount="1">
-  <autoFilter ref="A6:N236"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DatiHEPscape" displayName="DatiHEPscape" ref="A6:N282" headerRowCount="1">
+  <autoFilter ref="A6:N282"/>
   <tableColumns count="14">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Q1"/>
@@ -187,8 +187,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="OriginaliHEPscape" displayName="OriginaliHEPscape" ref="A1:R231" headerRowCount="1">
-  <autoFilter ref="A1:R231"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="OriginaliHEPscape" displayName="OriginaliHEPscape" ref="A1:R277" headerRowCount="1">
+  <autoFilter ref="A1:R277"/>
   <tableColumns count="18">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Q1"/>
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N236"/>
+  <dimension ref="A1:N282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HEPscape! | Evento ERNEST - ERN 2026 | 230 questionari</t>
+          <t>HEPscape! | Evento ERNEST - ERN 2026 | 276 questionari</t>
         </is>
       </c>
     </row>
@@ -12623,44 +12623,2432 @@
         </is>
       </c>
     </row>
+    <row r="237" ht="34" customHeight="1">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-001</t>
+        </is>
+      </c>
+      <c r="B237" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C237" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE ISTRUTTIVA</t>
+        </is>
+      </c>
+      <c r="D237" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F237" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I237" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J237" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="L237" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M237" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N237" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="34" customHeight="1">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-002</t>
+        </is>
+      </c>
+      <c r="B238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C238" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE E ISTRUTTIVA</t>
+        </is>
+      </c>
+      <c r="D238" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L238" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M238" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N238" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="34" customHeight="1">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-003</t>
+        </is>
+      </c>
+      <c r="B239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C239" s="1" t="inlineStr">
+        <is>
+          <t>BELLISSIMO GRAZIE</t>
+        </is>
+      </c>
+      <c r="D239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I239" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K239" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L239" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M239" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N239" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="34" customHeight="1">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-004</t>
+        </is>
+      </c>
+      <c r="B240" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C240" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE E TI FA IMPARARE INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D240" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F240" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G240" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I240" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J240" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K240" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L240" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M240" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N240" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="34" customHeight="1">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-005</t>
+        </is>
+      </c>
+      <c r="B241" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C241" s="1" t="inlineStr">
+        <is>
+          <t>CARINA EDUCATIVO PER I BAMBINI</t>
+        </is>
+      </c>
+      <c r="D241" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E241" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F241" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I241" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L241" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M241" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N241" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="34" customHeight="1">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-006</t>
+        </is>
+      </c>
+      <c r="B242" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" s="1" t="inlineStr">
+        <is>
+          <t>ISTRUTTIVA, DIVERTENTE, CURIOSA</t>
+        </is>
+      </c>
+      <c r="D242" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I242" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L242" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M242" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N242" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="34" customHeight="1">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-007</t>
+        </is>
+      </c>
+      <c r="B243" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C243" s="1" t="inlineStr">
+        <is>
+          <t>BELLISSIMA</t>
+        </is>
+      </c>
+      <c r="D243" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I243" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L243" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M243" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N243" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="34" customHeight="1">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-008</t>
+        </is>
+      </c>
+      <c r="B244" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C244" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D244" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E244" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F244" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I244" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L244" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M244" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N244" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="34" customHeight="1">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-009</t>
+        </is>
+      </c>
+      <c r="B245" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" s="1" t="inlineStr">
+        <is>
+          <t>MI È PIACIUTA TANTO</t>
+        </is>
+      </c>
+      <c r="D245" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E245" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F245" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H245" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I245" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="J245" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K245" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M245" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N245" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="34" customHeight="1">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-010</t>
+        </is>
+      </c>
+      <c r="B246" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C246" s="1" t="inlineStr">
+        <is>
+          <t>PROTONE, QUARK</t>
+        </is>
+      </c>
+      <c r="D246" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E246" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H246" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I246" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K246" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L246" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M246" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N246" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="34" customHeight="1">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-011</t>
+        </is>
+      </c>
+      <c r="B247" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C247" s="1" t="inlineStr">
+        <is>
+          <t>CURIOSITÀ, SCOPERTE</t>
+        </is>
+      </c>
+      <c r="D247" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G247" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I247" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K247" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L247" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M247" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N247" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="34" customHeight="1">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-012</t>
+        </is>
+      </c>
+      <c r="B248" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C248" s="1" t="inlineStr">
+        <is>
+          <t>FICA, GANZA</t>
+        </is>
+      </c>
+      <c r="D248" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E248" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F248" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H248" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="I248" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="J248" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K248" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L248" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M248" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N248" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="34" customHeight="1">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-013</t>
+        </is>
+      </c>
+      <c r="B249" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C249" s="1" t="inlineStr">
+        <is>
+          <t>CARINA, INTERESSANTE, PIACEVOLE</t>
+        </is>
+      </c>
+      <c r="D249" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E249" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F249" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G249" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I249" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J249" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L249" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M249" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N249" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="34" customHeight="1">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-014</t>
+        </is>
+      </c>
+      <c r="B250" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C250" s="1" t="inlineStr">
+        <is>
+          <t>FORMATIVA, INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D250" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I250" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J250" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L250" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M250" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N250" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="34" customHeight="1">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-015</t>
+        </is>
+      </c>
+      <c r="B251" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C251" s="1" t="inlineStr">
+        <is>
+          <t>SIMPATICA, DIVERTENTE, CURIOSA</t>
+        </is>
+      </c>
+      <c r="D251" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H251" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="I251" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J251" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L251" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M251" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N251" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="34" customHeight="1">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-016</t>
+        </is>
+      </c>
+      <c r="B252" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C252" s="1" t="inlineStr">
+        <is>
+          <t>BELLA INTERESSANTE E DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D252" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F252" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H252" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I252" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J252" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K252" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L252" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M252" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N252" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="34" customHeight="1">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-017</t>
+        </is>
+      </c>
+      <c r="B253" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C253" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE, BELLO</t>
+        </is>
+      </c>
+      <c r="D253" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G253" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I253" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J253" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K253" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L253" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M253" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N253" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="34" customHeight="1">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-018</t>
+        </is>
+      </c>
+      <c r="B254" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C254" s="1" t="inlineStr">
+        <is>
+          <t>FICO</t>
+        </is>
+      </c>
+      <c r="D254" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E254" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H254" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I254" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K254" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M254" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N254" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="34" customHeight="1">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-019</t>
+        </is>
+      </c>
+      <c r="B255" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C255" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE, SIMPATICO</t>
+        </is>
+      </c>
+      <c r="D255" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I255" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J255" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L255" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M255" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N255" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="34" customHeight="1">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-020</t>
+        </is>
+      </c>
+      <c r="B256" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C256" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D256" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I256" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J256" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L256" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M256" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N256" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="34" customHeight="1">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-021</t>
+        </is>
+      </c>
+      <c r="B257" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C257" s="1" t="inlineStr">
+        <is>
+          <t>BELLA, CURIOSA E MOLTO COMPLESSA</t>
+        </is>
+      </c>
+      <c r="D257" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E257" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F257" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G257" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H257" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I257" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L257" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M257" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N257" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="34" customHeight="1">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-022</t>
+        </is>
+      </c>
+      <c r="B258" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C258" s="1" t="inlineStr">
+        <is>
+          <t>INTERESANTE</t>
+        </is>
+      </c>
+      <c r="D258" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I258" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J258" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K258" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M258" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N258" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="34" customHeight="1">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-023</t>
+        </is>
+      </c>
+      <c r="B259" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C259" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE, EDUCATIVA E DINAMICA</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E259" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F259" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I259" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J259" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L259" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M259" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N259" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="34" customHeight="1">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-024</t>
+        </is>
+      </c>
+      <c r="B260" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C260" s="1" t="inlineStr">
+        <is>
+          <t>PARTICOLARE, INNOVATIVA, CURIOSA</t>
+        </is>
+      </c>
+      <c r="D260" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E260" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F260" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G260" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I260" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J260" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L260" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M260" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N260" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="34" customHeight="1">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-025</t>
+        </is>
+      </c>
+      <c r="B261" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C261" s="1" t="inlineStr">
+        <is>
+          <t>AFFASCINANTE, INTERESSANTE, EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="D261" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F261" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H261" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I261" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L261" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M261" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N261" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="34" customHeight="1">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-026</t>
+        </is>
+      </c>
+      <c r="B262" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C262" s="1" t="inlineStr">
+        <is>
+          <t>BELLA DIVERTIMENTO</t>
+        </is>
+      </c>
+      <c r="D262" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E262" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F262" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H262" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I262" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K262" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L262" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M262" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N262" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="34" customHeight="1">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-027</t>
+        </is>
+      </c>
+      <c r="B263" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C263" s="1" t="inlineStr">
+        <is>
+          <t>UNICA SEMPLICE</t>
+        </is>
+      </c>
+      <c r="D263" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F263" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I263" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J263" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K263" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L263" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M263" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N263" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="34" customHeight="1">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-028</t>
+        </is>
+      </c>
+      <c r="B264" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C264" s="1" t="inlineStr">
+        <is>
+          <t>CARINA, DIVERSA</t>
+        </is>
+      </c>
+      <c r="D264" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F264" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G264" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H264" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I264" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J264" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L264" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M264" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N264" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="34" customHeight="1">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-029</t>
+        </is>
+      </c>
+      <c r="B265" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C265" s="1" t="inlineStr">
+        <is>
+          <t>CARINA PARTICOLARE</t>
+        </is>
+      </c>
+      <c r="D265" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E265" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F265" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I265" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J265" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L265" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M265" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N265" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="34" customHeight="1">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-030</t>
+        </is>
+      </c>
+      <c r="B266" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C266" s="1" t="inlineStr">
+        <is>
+          <t>CARINA DIVERSA</t>
+        </is>
+      </c>
+      <c r="D266" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E266" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F266" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H266" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I266" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J266" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L266" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M266" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N266" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="34" customHeight="1">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-031</t>
+        </is>
+      </c>
+      <c r="B267" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C267" s="1" t="inlineStr">
+        <is>
+          <t>INFORMATIVA DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D267" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F267" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G267" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I267" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J267" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L267" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M267" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N267" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="34" customHeight="1">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-032</t>
+        </is>
+      </c>
+      <c r="B268" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C268" s="1" t="inlineStr">
+        <is>
+          <t>UNICA, FACILE</t>
+        </is>
+      </c>
+      <c r="D268" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H268" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I268" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J268" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L268" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M268" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N268" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="34" customHeight="1">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-033</t>
+        </is>
+      </c>
+      <c r="B269" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C269" s="1" t="inlineStr">
+        <is>
+          <t>CREATIVA DIVERTENTE, COINVOLGENTE</t>
+        </is>
+      </c>
+      <c r="D269" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F269" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G269" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I269" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J269" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K269" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L269" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M269" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N269" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="34" customHeight="1">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-034</t>
+        </is>
+      </c>
+      <c r="B270" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C270" s="1" t="inlineStr">
+        <is>
+          <t>CREATIVA, DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D270" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F270" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G270" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I270" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L270" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M270" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N270" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="34" customHeight="1">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-035</t>
+        </is>
+      </c>
+      <c r="B271" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C271" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE DIVERSA</t>
+        </is>
+      </c>
+      <c r="D271" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F271" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H271" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I271" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J271" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L271" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M271" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N271" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="34" customHeight="1">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-036</t>
+        </is>
+      </c>
+      <c r="B272" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C272" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE E MOLTO ISTRUTTIVA</t>
+        </is>
+      </c>
+      <c r="D272" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F272" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I272" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J272" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L272" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M272" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N272" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="34" customHeight="1">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-037</t>
+        </is>
+      </c>
+      <c r="B273" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C273" s="1" t="inlineStr">
+        <is>
+          <t>STUPENDA, SPETTACOLARE</t>
+        </is>
+      </c>
+      <c r="D273" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F273" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I273" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J273" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K273" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L273" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M273" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N273" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="34" customHeight="1">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-038</t>
+        </is>
+      </c>
+      <c r="B274" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C274" s="1" t="inlineStr">
+        <is>
+          <t>INTERATTIVA, COINVOLGENTE E DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D274" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F274" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G274" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H274" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I274" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K274" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L274" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M274" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N274" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="34" customHeight="1">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-039</t>
+        </is>
+      </c>
+      <c r="B275" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C275" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D275" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E275" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F275" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G275" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I275" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J275" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K275" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L275" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M275" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N275" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="34" customHeight="1">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-040</t>
+        </is>
+      </c>
+      <c r="B276" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C276" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE-DIVERTENTE-INTERATTIVA</t>
+        </is>
+      </c>
+      <c r="D276" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F276" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G276" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I276" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J276" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K276" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L276" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M276" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N276" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="34" customHeight="1">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-041</t>
+        </is>
+      </c>
+      <c r="B277" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C277" s="1" t="inlineStr">
+        <is>
+          <t>COLLABORAZIONE, COINVOLGIMENTO, DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D277" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E277" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F277" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H277" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I277" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J277" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L277" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M277" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N277" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="34" customHeight="1">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-042</t>
+        </is>
+      </c>
+      <c r="B278" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C278" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE, INTERESSANTE, CARINA</t>
+        </is>
+      </c>
+      <c r="D278" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E278" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F278" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G278" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H278" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I278" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L278" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M278" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N278" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="34" customHeight="1">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-043</t>
+        </is>
+      </c>
+      <c r="B279" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C279" s="1" t="inlineStr">
+        <is>
+          <t>COINVOLGENTE, INTERESSANTE, DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D279" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I279" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K279" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L279" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M279" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N279" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="34" customHeight="1">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-044</t>
+        </is>
+      </c>
+      <c r="B280" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C280" s="1" t="inlineStr">
+        <is>
+          <t>BELLISSIMA DIVERTENTISSIMA SUPER</t>
+        </is>
+      </c>
+      <c r="D280" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F280" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I280" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K280" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L280" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M280" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N280" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="34" customHeight="1">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-045</t>
+        </is>
+      </c>
+      <c r="B281" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C281" s="1" t="inlineStr">
+        <is>
+          <t>AVVINCENTE-COINVOLGENTE-INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D281" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H281" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I281" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J281" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K281" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L281" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M281" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N281" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="34" customHeight="1">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-046</t>
+        </is>
+      </c>
+      <c r="B282" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C282" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE BELLO</t>
+        </is>
+      </c>
+      <c r="D282" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E282" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H282" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I282" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J282" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K282" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L282" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M282" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="N282" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B7:L236">
+  <conditionalFormatting sqref="B7:L282">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>999</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="10">
-    <dataValidation sqref="B7:B236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="B7:B282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:D236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="D7:D282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="E7:E236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="E7:E282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="F7:F236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="F7:F282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="G7:G236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="G7:G282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="H7:H236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="H7:H282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="I7:I236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="I7:I282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="J7:J236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="J7:J282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,3,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="K7:K236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="K7:K282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,3,4,5,6,7,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="L7:L236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="L7:L282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,999"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12677,7 +15065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R231"/>
+  <dimension ref="A1:R277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -31861,6 +34249,3867 @@
       </c>
       <c r="R231" s="1" t="inlineStr"/>
     </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-001</t>
+        </is>
+      </c>
+      <c r="B232" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C232" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE ISTRUTTIVA</t>
+        </is>
+      </c>
+      <c r="D232" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E232" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F232" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G232" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H232" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I232" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J232" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K232" s="1" t="inlineStr">
+        <is>
+          <t>Preferisco non rispondere</t>
+        </is>
+      </c>
+      <c r="L232" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M232" s="1" t="inlineStr"/>
+      <c r="N232" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=1</t>
+        </is>
+      </c>
+      <c r="O232" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P232" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q232" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R232" s="1" t="inlineStr"/>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-002</t>
+        </is>
+      </c>
+      <c r="B233" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C233" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE E ISTRUTTIVA</t>
+        </is>
+      </c>
+      <c r="D233" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E233" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F233" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G233" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H233" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I233" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J233" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K233" s="1" t="inlineStr">
+        <is>
+          <t>Più di 60</t>
+        </is>
+      </c>
+      <c r="L233" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M233" s="1" t="inlineStr"/>
+      <c r="N233" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=2</t>
+        </is>
+      </c>
+      <c r="O233" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P233" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q233" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R233" s="1" t="inlineStr"/>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-003</t>
+        </is>
+      </c>
+      <c r="B234" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C234" s="1" t="inlineStr">
+        <is>
+          <t>BELLISSIMO GRAZIE</t>
+        </is>
+      </c>
+      <c r="D234" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E234" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F234" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G234" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H234" s="1" t="inlineStr">
+        <is>
+          <t>Spesso</t>
+        </is>
+      </c>
+      <c r="I234" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J234" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K234" s="1" t="inlineStr">
+        <is>
+          <t>19–25</t>
+        </is>
+      </c>
+      <c r="L234" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M234" s="1" t="inlineStr"/>
+      <c r="N234" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=3</t>
+        </is>
+      </c>
+      <c r="O234" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P234" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q234" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R234" s="1" t="inlineStr"/>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-004</t>
+        </is>
+      </c>
+      <c r="B235" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C235" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE E TI FA IMPARARE INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D235" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E235" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F235" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G235" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H235" s="1" t="inlineStr">
+        <is>
+          <t>Spesso</t>
+        </is>
+      </c>
+      <c r="I235" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J235" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K235" s="1" t="inlineStr">
+        <is>
+          <t>26–40</t>
+        </is>
+      </c>
+      <c r="L235" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M235" s="1" t="inlineStr"/>
+      <c r="N235" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=4</t>
+        </is>
+      </c>
+      <c r="O235" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P235" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q235" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R235" s="1" t="inlineStr"/>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-005</t>
+        </is>
+      </c>
+      <c r="B236" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C236" s="1" t="inlineStr">
+        <is>
+          <t>CARINA EDUCATIVO PER I BAMBINI</t>
+        </is>
+      </c>
+      <c r="D236" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E236" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F236" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G236" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H236" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I236" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J236" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K236" s="1" t="inlineStr">
+        <is>
+          <t>26–40</t>
+        </is>
+      </c>
+      <c r="L236" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M236" s="1" t="inlineStr"/>
+      <c r="N236" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=5</t>
+        </is>
+      </c>
+      <c r="O236" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P236" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q236" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R236" s="1" t="inlineStr"/>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-006</t>
+        </is>
+      </c>
+      <c r="B237" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C237" s="1" t="inlineStr">
+        <is>
+          <t>ISTRUTTIVA, DIVERTENTE, CURIOSA</t>
+        </is>
+      </c>
+      <c r="D237" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E237" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F237" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G237" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H237" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I237" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J237" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K237" s="1" t="inlineStr">
+        <is>
+          <t>26–40</t>
+        </is>
+      </c>
+      <c r="L237" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M237" s="1" t="inlineStr"/>
+      <c r="N237" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=6</t>
+        </is>
+      </c>
+      <c r="O237" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P237" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q237" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R237" s="1" t="inlineStr"/>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-007</t>
+        </is>
+      </c>
+      <c r="B238" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C238" s="1" t="inlineStr">
+        <is>
+          <t>BELLISSIMA</t>
+        </is>
+      </c>
+      <c r="D238" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E238" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F238" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G238" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H238" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I238" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J238" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K238" s="1" t="inlineStr">
+        <is>
+          <t>19–25</t>
+        </is>
+      </c>
+      <c r="L238" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M238" s="1" t="inlineStr"/>
+      <c r="N238" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=7</t>
+        </is>
+      </c>
+      <c r="O238" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P238" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q238" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R238" s="1" t="inlineStr"/>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-008</t>
+        </is>
+      </c>
+      <c r="B239" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C239" s="1" t="inlineStr"/>
+      <c r="D239" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E239" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F239" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G239" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H239" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I239" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J239" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K239" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L239" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M239" s="1" t="inlineStr"/>
+      <c r="N239" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=8</t>
+        </is>
+      </c>
+      <c r="O239" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P239" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q239" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R239" s="1" t="inlineStr"/>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-009</t>
+        </is>
+      </c>
+      <c r="B240" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C240" s="1" t="inlineStr">
+        <is>
+          <t>MI È PIACIUTA TANTO</t>
+        </is>
+      </c>
+      <c r="D240" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E240" s="1" t="inlineStr">
+        <is>
+          <t>Meno curioso/a</t>
+        </is>
+      </c>
+      <c r="F240" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G240" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H240" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I240" s="1" t="inlineStr"/>
+      <c r="J240" s="1" t="inlineStr">
+        <is>
+          <t>Preferisco non rispondere</t>
+        </is>
+      </c>
+      <c r="K240" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L240" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M240" s="1" t="inlineStr"/>
+      <c r="N240" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=9</t>
+        </is>
+      </c>
+      <c r="O240" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P240" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q240" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R240" s="1" t="inlineStr"/>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-010</t>
+        </is>
+      </c>
+      <c r="B241" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C241" s="1" t="inlineStr">
+        <is>
+          <t>PROTONE, QUARK</t>
+        </is>
+      </c>
+      <c r="D241" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E241" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F241" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G241" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H241" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I241" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J241" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K241" s="1" t="inlineStr">
+        <is>
+          <t>41–60</t>
+        </is>
+      </c>
+      <c r="L241" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M241" s="1" t="inlineStr"/>
+      <c r="N241" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=10</t>
+        </is>
+      </c>
+      <c r="O241" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P241" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q241" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R241" s="1" t="inlineStr"/>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-011</t>
+        </is>
+      </c>
+      <c r="B242" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C242" s="1" t="inlineStr">
+        <is>
+          <t>CURIOSITÀ, SCOPERTE</t>
+        </is>
+      </c>
+      <c r="D242" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E242" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F242" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G242" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H242" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I242" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J242" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K242" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L242" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M242" s="1" t="inlineStr"/>
+      <c r="N242" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=11</t>
+        </is>
+      </c>
+      <c r="O242" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P242" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q242" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R242" s="1" t="inlineStr"/>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-012</t>
+        </is>
+      </c>
+      <c r="B243" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C243" s="1" t="inlineStr">
+        <is>
+          <t>FICA, GANZA</t>
+        </is>
+      </c>
+      <c r="D243" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E243" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F243" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G243" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H243" s="1" t="inlineStr"/>
+      <c r="I243" s="1" t="inlineStr"/>
+      <c r="J243" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K243" s="1" t="inlineStr">
+        <is>
+          <t>11–14</t>
+        </is>
+      </c>
+      <c r="L243" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M243" s="1" t="inlineStr"/>
+      <c r="N243" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=12</t>
+        </is>
+      </c>
+      <c r="O243" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P243" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q243" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R243" s="1" t="inlineStr"/>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-013</t>
+        </is>
+      </c>
+      <c r="B244" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C244" s="1" t="inlineStr">
+        <is>
+          <t>CARINA, INTERESSANTE, PIACEVOLE</t>
+        </is>
+      </c>
+      <c r="D244" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E244" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F244" s="1" t="inlineStr">
+        <is>
+          <t>Meno interessato/a</t>
+        </is>
+      </c>
+      <c r="G244" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H244" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I244" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J244" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K244" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L244" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M244" s="1" t="inlineStr"/>
+      <c r="N244" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=13</t>
+        </is>
+      </c>
+      <c r="O244" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P244" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q244" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R244" s="1" t="inlineStr"/>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-014</t>
+        </is>
+      </c>
+      <c r="B245" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C245" s="1" t="inlineStr">
+        <is>
+          <t>FORMATIVA, INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D245" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E245" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F245" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G245" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H245" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I245" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J245" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K245" s="1" t="inlineStr">
+        <is>
+          <t>19–25</t>
+        </is>
+      </c>
+      <c r="L245" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M245" s="1" t="inlineStr"/>
+      <c r="N245" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=14</t>
+        </is>
+      </c>
+      <c r="O245" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P245" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q245" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R245" s="1" t="inlineStr"/>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-015</t>
+        </is>
+      </c>
+      <c r="B246" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C246" s="1" t="inlineStr">
+        <is>
+          <t>SIMPATICA, DIVERTENTE, CURIOSA</t>
+        </is>
+      </c>
+      <c r="D246" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E246" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F246" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G246" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H246" s="1" t="inlineStr"/>
+      <c r="I246" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J246" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K246" s="1" t="inlineStr">
+        <is>
+          <t>41–60</t>
+        </is>
+      </c>
+      <c r="L246" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M246" s="1" t="inlineStr"/>
+      <c r="N246" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=15</t>
+        </is>
+      </c>
+      <c r="O246" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P246" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q246" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R246" s="1" t="inlineStr"/>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-016</t>
+        </is>
+      </c>
+      <c r="B247" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C247" s="1" t="inlineStr">
+        <is>
+          <t>BELLA INTERESSANTE E DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D247" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E247" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F247" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G247" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H247" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I247" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J247" s="1" t="inlineStr">
+        <is>
+          <t>Preferisco non rispondere</t>
+        </is>
+      </c>
+      <c r="K247" s="1" t="inlineStr">
+        <is>
+          <t>11–14</t>
+        </is>
+      </c>
+      <c r="L247" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M247" s="1" t="inlineStr"/>
+      <c r="N247" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=16</t>
+        </is>
+      </c>
+      <c r="O247" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P247" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q247" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R247" s="1" t="inlineStr"/>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-017</t>
+        </is>
+      </c>
+      <c r="B248" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C248" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE, BELLO</t>
+        </is>
+      </c>
+      <c r="D248" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E248" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F248" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G248" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H248" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I248" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J248" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K248" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L248" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M248" s="1" t="inlineStr"/>
+      <c r="N248" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=17</t>
+        </is>
+      </c>
+      <c r="O248" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P248" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q248" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R248" s="1" t="inlineStr"/>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-018</t>
+        </is>
+      </c>
+      <c r="B249" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C249" s="1" t="inlineStr">
+        <is>
+          <t>FICO</t>
+        </is>
+      </c>
+      <c r="D249" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E249" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F249" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G249" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H249" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I249" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J249" s="1" t="inlineStr">
+        <is>
+          <t>Altro</t>
+        </is>
+      </c>
+      <c r="K249" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L249" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M249" s="1" t="inlineStr">
+        <is>
+          <t>Q6: Punto A: risposta chiarita dall’utente in chat il 2026-10-01.</t>
+        </is>
+      </c>
+      <c r="N249" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=18</t>
+        </is>
+      </c>
+      <c r="O249" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P249" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q249" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R249" s="1" t="inlineStr"/>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-019</t>
+        </is>
+      </c>
+      <c r="B250" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C250" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE, SIMPATICO</t>
+        </is>
+      </c>
+      <c r="D250" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E250" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F250" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G250" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H250" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I250" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J250" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K250" s="1" t="inlineStr">
+        <is>
+          <t>11–14</t>
+        </is>
+      </c>
+      <c r="L250" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M250" s="1" t="inlineStr"/>
+      <c r="N250" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=19</t>
+        </is>
+      </c>
+      <c r="O250" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P250" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q250" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R250" s="1" t="inlineStr"/>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-020</t>
+        </is>
+      </c>
+      <c r="B251" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C251" s="1" t="inlineStr"/>
+      <c r="D251" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E251" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F251" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G251" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H251" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I251" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J251" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K251" s="1" t="inlineStr">
+        <is>
+          <t>Più di 60</t>
+        </is>
+      </c>
+      <c r="L251" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M251" s="1" t="inlineStr">
+        <is>
+          <t>Q7: Punto B: risposta chiarita dall’utente in chat il 2026-10-01.</t>
+        </is>
+      </c>
+      <c r="N251" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=20</t>
+        </is>
+      </c>
+      <c r="O251" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P251" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q251" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R251" s="1" t="inlineStr"/>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-021</t>
+        </is>
+      </c>
+      <c r="B252" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C252" s="1" t="inlineStr">
+        <is>
+          <t>BELLA, CURIOSA E MOLTO COMPLESSA</t>
+        </is>
+      </c>
+      <c r="D252" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E252" s="1" t="inlineStr">
+        <is>
+          <t>Meno curioso/a</t>
+        </is>
+      </c>
+      <c r="F252" s="1" t="inlineStr">
+        <is>
+          <t>Meno interessato/a</t>
+        </is>
+      </c>
+      <c r="G252" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H252" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I252" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J252" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K252" s="1" t="inlineStr">
+        <is>
+          <t>11–14</t>
+        </is>
+      </c>
+      <c r="L252" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M252" s="1" t="inlineStr"/>
+      <c r="N252" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=21</t>
+        </is>
+      </c>
+      <c r="O252" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P252" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q252" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R252" s="1" t="inlineStr"/>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-022</t>
+        </is>
+      </c>
+      <c r="B253" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C253" s="1" t="inlineStr">
+        <is>
+          <t>INTERESANTE</t>
+        </is>
+      </c>
+      <c r="D253" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E253" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F253" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G253" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H253" s="1" t="inlineStr">
+        <is>
+          <t>Spesso</t>
+        </is>
+      </c>
+      <c r="I253" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J253" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K253" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L253" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M253" s="1" t="inlineStr"/>
+      <c r="N253" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=22</t>
+        </is>
+      </c>
+      <c r="O253" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P253" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q253" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R253" s="1" t="inlineStr"/>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-023</t>
+        </is>
+      </c>
+      <c r="B254" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C254" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE, EDUCATIVA E DINAMICA</t>
+        </is>
+      </c>
+      <c r="D254" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E254" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F254" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G254" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H254" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I254" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J254" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K254" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L254" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M254" s="1" t="inlineStr"/>
+      <c r="N254" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=23</t>
+        </is>
+      </c>
+      <c r="O254" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P254" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q254" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R254" s="1" t="inlineStr"/>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-024</t>
+        </is>
+      </c>
+      <c r="B255" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C255" s="1" t="inlineStr">
+        <is>
+          <t>PARTICOLARE, INNOVATIVA, CURIOSA</t>
+        </is>
+      </c>
+      <c r="D255" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E255" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F255" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G255" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H255" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I255" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J255" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K255" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L255" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M255" s="1" t="inlineStr"/>
+      <c r="N255" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=24</t>
+        </is>
+      </c>
+      <c r="O255" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P255" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q255" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R255" s="1" t="inlineStr"/>
+    </row>
+    <row r="256" ht="52" customHeight="1">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-025</t>
+        </is>
+      </c>
+      <c r="B256" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C256" s="1" t="inlineStr">
+        <is>
+          <t>AFFASCINANTE, INTERESSANTE, EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="D256" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E256" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F256" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G256" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H256" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I256" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J256" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K256" s="1" t="inlineStr">
+        <is>
+          <t>26–40</t>
+        </is>
+      </c>
+      <c r="L256" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M256" s="1" t="inlineStr">
+        <is>
+          <t>Q1: Punto C: risposta chiarita dall’utente in chat il 2026-10-01.
+Q6: Punto D: risposta chiarita dall’utente in chat il 2026-10-01.</t>
+        </is>
+      </c>
+      <c r="N256" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=25</t>
+        </is>
+      </c>
+      <c r="O256" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P256" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q256" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R256" s="1" t="inlineStr"/>
+    </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-026</t>
+        </is>
+      </c>
+      <c r="B257" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C257" s="1" t="inlineStr">
+        <is>
+          <t>BELLA DIVERTIMENTO</t>
+        </is>
+      </c>
+      <c r="D257" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E257" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F257" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G257" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H257" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I257" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J257" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K257" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L257" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M257" s="1" t="inlineStr">
+        <is>
+          <t>Q10: Punto E: risposta chiarita dall’utente in chat il 2026-10-01.</t>
+        </is>
+      </c>
+      <c r="N257" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=26</t>
+        </is>
+      </c>
+      <c r="O257" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P257" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q257" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R257" s="1" t="inlineStr"/>
+    </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-027</t>
+        </is>
+      </c>
+      <c r="B258" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C258" s="1" t="inlineStr">
+        <is>
+          <t>UNICA SEMPLICE</t>
+        </is>
+      </c>
+      <c r="D258" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E258" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F258" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G258" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H258" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I258" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J258" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K258" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L258" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M258" s="1" t="inlineStr"/>
+      <c r="N258" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=27</t>
+        </is>
+      </c>
+      <c r="O258" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P258" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q258" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R258" s="1" t="inlineStr"/>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-028</t>
+        </is>
+      </c>
+      <c r="B259" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C259" s="1" t="inlineStr">
+        <is>
+          <t>CARINA, DIVERSA</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E259" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F259" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G259" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H259" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I259" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J259" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K259" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L259" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M259" s="1" t="inlineStr"/>
+      <c r="N259" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=28</t>
+        </is>
+      </c>
+      <c r="O259" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P259" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q259" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R259" s="1" t="inlineStr"/>
+    </row>
+    <row r="260" ht="40" customHeight="1">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-029</t>
+        </is>
+      </c>
+      <c r="B260" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C260" s="1" t="inlineStr">
+        <is>
+          <t>CARINA PARTICOLARE</t>
+        </is>
+      </c>
+      <c r="D260" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E260" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F260" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G260" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H260" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I260" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J260" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K260" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L260" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M260" s="1" t="inlineStr"/>
+      <c r="N260" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=29</t>
+        </is>
+      </c>
+      <c r="O260" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P260" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q260" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R260" s="1" t="inlineStr"/>
+    </row>
+    <row r="261" ht="40" customHeight="1">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-030</t>
+        </is>
+      </c>
+      <c r="B261" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C261" s="1" t="inlineStr">
+        <is>
+          <t>CARINA DIVERSA</t>
+        </is>
+      </c>
+      <c r="D261" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E261" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F261" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G261" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H261" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I261" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J261" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K261" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L261" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M261" s="1" t="inlineStr"/>
+      <c r="N261" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=30</t>
+        </is>
+      </c>
+      <c r="O261" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P261" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q261" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R261" s="1" t="inlineStr"/>
+    </row>
+    <row r="262" ht="40" customHeight="1">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-031</t>
+        </is>
+      </c>
+      <c r="B262" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C262" s="1" t="inlineStr">
+        <is>
+          <t>INFORMATIVA DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D262" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E262" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F262" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G262" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H262" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I262" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J262" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K262" s="1" t="inlineStr">
+        <is>
+          <t>41–60</t>
+        </is>
+      </c>
+      <c r="L262" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M262" s="1" t="inlineStr"/>
+      <c r="N262" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=31</t>
+        </is>
+      </c>
+      <c r="O262" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P262" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q262" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R262" s="1" t="inlineStr"/>
+    </row>
+    <row r="263" ht="40" customHeight="1">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-032</t>
+        </is>
+      </c>
+      <c r="B263" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C263" s="1" t="inlineStr">
+        <is>
+          <t>UNICA, FACILE</t>
+        </is>
+      </c>
+      <c r="D263" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E263" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F263" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G263" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H263" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I263" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J263" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K263" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L263" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M263" s="1" t="inlineStr"/>
+      <c r="N263" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=32</t>
+        </is>
+      </c>
+      <c r="O263" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P263" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q263" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R263" s="1" t="inlineStr"/>
+    </row>
+    <row r="264" ht="40" customHeight="1">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-033</t>
+        </is>
+      </c>
+      <c r="B264" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C264" s="1" t="inlineStr">
+        <is>
+          <t>CREATIVA DIVERTENTE, COINVOLGENTE</t>
+        </is>
+      </c>
+      <c r="D264" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E264" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F264" s="1" t="inlineStr">
+        <is>
+          <t>Meno interessato/a</t>
+        </is>
+      </c>
+      <c r="G264" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H264" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I264" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J264" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K264" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L264" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M264" s="1" t="inlineStr"/>
+      <c r="N264" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=33</t>
+        </is>
+      </c>
+      <c r="O264" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P264" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q264" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R264" s="1" t="inlineStr"/>
+    </row>
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-034</t>
+        </is>
+      </c>
+      <c r="B265" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C265" s="1" t="inlineStr">
+        <is>
+          <t>CREATIVA, DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D265" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E265" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F265" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G265" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H265" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I265" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J265" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K265" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L265" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M265" s="1" t="inlineStr"/>
+      <c r="N265" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=34</t>
+        </is>
+      </c>
+      <c r="O265" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P265" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q265" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R265" s="1" t="inlineStr"/>
+    </row>
+    <row r="266" ht="40" customHeight="1">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-035</t>
+        </is>
+      </c>
+      <c r="B266" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C266" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE DIVERSA</t>
+        </is>
+      </c>
+      <c r="D266" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E266" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F266" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G266" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H266" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I266" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J266" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K266" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L266" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M266" s="1" t="inlineStr"/>
+      <c r="N266" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=35</t>
+        </is>
+      </c>
+      <c r="O266" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P266" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q266" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R266" s="1" t="inlineStr"/>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-036</t>
+        </is>
+      </c>
+      <c r="B267" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C267" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE E MOLTO ISTRUTTIVA</t>
+        </is>
+      </c>
+      <c r="D267" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E267" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F267" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G267" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H267" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I267" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J267" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K267" s="1" t="inlineStr">
+        <is>
+          <t>41–60</t>
+        </is>
+      </c>
+      <c r="L267" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M267" s="1" t="inlineStr"/>
+      <c r="N267" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=36</t>
+        </is>
+      </c>
+      <c r="O267" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P267" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q267" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R267" s="1" t="inlineStr"/>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-037</t>
+        </is>
+      </c>
+      <c r="B268" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C268" s="1" t="inlineStr">
+        <is>
+          <t>STUPENDA, SPETTACOLARE</t>
+        </is>
+      </c>
+      <c r="D268" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E268" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F268" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G268" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H268" s="1" t="inlineStr">
+        <is>
+          <t>Spesso</t>
+        </is>
+      </c>
+      <c r="I268" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J268" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K268" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L268" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M268" s="1" t="inlineStr"/>
+      <c r="N268" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=37</t>
+        </is>
+      </c>
+      <c r="O268" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P268" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q268" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R268" s="1" t="inlineStr"/>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-038</t>
+        </is>
+      </c>
+      <c r="B269" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C269" s="1" t="inlineStr">
+        <is>
+          <t>INTERATTIVA, COINVOLGENTE E DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D269" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E269" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F269" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G269" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H269" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I269" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J269" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K269" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L269" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M269" s="1" t="inlineStr"/>
+      <c r="N269" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=38</t>
+        </is>
+      </c>
+      <c r="O269" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P269" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q269" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R269" s="1" t="inlineStr"/>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-039</t>
+        </is>
+      </c>
+      <c r="B270" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C270" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D270" s="1" t="inlineStr">
+        <is>
+          <t>No, per niente</t>
+        </is>
+      </c>
+      <c r="E270" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F270" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G270" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H270" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I270" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J270" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K270" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L270" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M270" s="1" t="inlineStr"/>
+      <c r="N270" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=39</t>
+        </is>
+      </c>
+      <c r="O270" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P270" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q270" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R270" s="1" t="inlineStr"/>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-040</t>
+        </is>
+      </c>
+      <c r="B271" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C271" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE-DIVERTENTE-INTERATTIVA</t>
+        </is>
+      </c>
+      <c r="D271" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E271" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F271" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G271" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H271" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I271" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J271" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K271" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L271" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M271" s="1" t="inlineStr"/>
+      <c r="N271" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=40</t>
+        </is>
+      </c>
+      <c r="O271" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P271" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q271" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R271" s="1" t="inlineStr"/>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-041</t>
+        </is>
+      </c>
+      <c r="B272" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C272" s="1" t="inlineStr">
+        <is>
+          <t>COLLABORAZIONE, COINVOLGIMENTO, DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D272" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E272" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F272" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G272" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H272" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I272" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J272" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K272" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L272" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M272" s="1" t="inlineStr"/>
+      <c r="N272" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=41</t>
+        </is>
+      </c>
+      <c r="O272" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P272" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q272" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R272" s="1" t="inlineStr"/>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-042</t>
+        </is>
+      </c>
+      <c r="B273" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C273" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE, INTERESSANTE, CARINA</t>
+        </is>
+      </c>
+      <c r="D273" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E273" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F273" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G273" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H273" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I273" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J273" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K273" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L273" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M273" s="1" t="inlineStr"/>
+      <c r="N273" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=42</t>
+        </is>
+      </c>
+      <c r="O273" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P273" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q273" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R273" s="1" t="inlineStr"/>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-043</t>
+        </is>
+      </c>
+      <c r="B274" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C274" s="1" t="inlineStr">
+        <is>
+          <t>COINVOLGENTE, INTERESSANTE, DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D274" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E274" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F274" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G274" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H274" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I274" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J274" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K274" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L274" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M274" s="1" t="inlineStr"/>
+      <c r="N274" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=43</t>
+        </is>
+      </c>
+      <c r="O274" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P274" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q274" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R274" s="1" t="inlineStr"/>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-044</t>
+        </is>
+      </c>
+      <c r="B275" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C275" s="1" t="inlineStr">
+        <is>
+          <t>BELLISSIMA DIVERTENTISSIMA SUPER</t>
+        </is>
+      </c>
+      <c r="D275" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E275" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F275" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G275" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H275" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I275" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J275" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K275" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L275" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M275" s="1" t="inlineStr"/>
+      <c r="N275" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=44</t>
+        </is>
+      </c>
+      <c r="O275" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P275" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q275" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R275" s="1" t="inlineStr"/>
+    </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-045</t>
+        </is>
+      </c>
+      <c r="B276" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C276" s="1" t="inlineStr">
+        <is>
+          <t>AVVINCENTE-COINVOLGENTE-INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D276" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E276" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F276" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G276" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H276" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I276" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J276" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K276" s="1" t="inlineStr">
+        <is>
+          <t>41–60</t>
+        </is>
+      </c>
+      <c r="L276" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M276" s="1" t="inlineStr"/>
+      <c r="N276" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=45</t>
+        </is>
+      </c>
+      <c r="O276" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P276" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q276" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R276" s="1" t="inlineStr"/>
+    </row>
+    <row r="277" ht="40" customHeight="1">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>PERUGIA-TERNI-046</t>
+        </is>
+      </c>
+      <c r="B277" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C277" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE BELLO</t>
+        </is>
+      </c>
+      <c r="D277" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E277" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F277" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G277" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H277" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I277" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J277" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K277" s="1" t="inlineStr">
+        <is>
+          <t>15–18</t>
+        </is>
+      </c>
+      <c r="L277" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M277" s="1" t="inlineStr">
+        <is>
+          <t>Q2: Punto F: risposta chiarita dall’utente in chat il 2026-10-01.</t>
+        </is>
+      </c>
+      <c r="N277" s="1" t="inlineStr">
+        <is>
+          <t>Survey1_Terni.pdf#page=46</t>
+        </is>
+      </c>
+      <c r="O277" s="1" t="inlineStr">
+        <is>
+          <t>Terni</t>
+        </is>
+      </c>
+      <c r="P277" s="1" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="Q277" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R277" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/ern2026/questionari.xlsx
+++ b/data/ern2026/questionari.xlsx
@@ -164,8 +164,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DatiHEPscape" displayName="DatiHEPscape" ref="A6:N282" headerRowCount="1">
-  <autoFilter ref="A6:N282"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DatiHEPscape" displayName="DatiHEPscape" ref="A6:N331" headerRowCount="1">
+  <autoFilter ref="A6:N331"/>
   <tableColumns count="14">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Q1"/>
@@ -187,8 +187,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="OriginaliHEPscape" displayName="OriginaliHEPscape" ref="A1:R277" headerRowCount="1">
-  <autoFilter ref="A1:R277"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="OriginaliHEPscape" displayName="OriginaliHEPscape" ref="A1:R326" headerRowCount="1">
+  <autoFilter ref="A1:R326"/>
   <tableColumns count="18">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Q1"/>
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N282"/>
+  <dimension ref="A1:N331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HEPscape! | Evento ERNEST - ERN 2026 | 276 questionari</t>
+          <t>HEPscape! | Evento ERNEST - ERN 2026 | 325 questionari</t>
         </is>
       </c>
     </row>
@@ -15011,44 +15011,2582 @@
         </is>
       </c>
     </row>
+    <row r="283" ht="34" customHeight="1">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-001</t>
+        </is>
+      </c>
+      <c r="B283" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C283" s="1" t="inlineStr">
+        <is>
+          <t>SENZAZIONALE</t>
+        </is>
+      </c>
+      <c r="D283" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E283" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F283" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G283" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H283" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I283" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K283" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L283" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M283" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N283" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="34" customHeight="1">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-002</t>
+        </is>
+      </c>
+      <c r="B284" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C284" s="1" t="inlineStr">
+        <is>
+          <t>APPASSIONANTE</t>
+        </is>
+      </c>
+      <c r="D284" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F284" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I284" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J284" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K284" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L284" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M284" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N284" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="34" customHeight="1">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-003</t>
+        </is>
+      </c>
+      <c r="B285" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C285" s="1" t="inlineStr">
+        <is>
+          <t>COINVOLGENTE SENSAZIONALE MISTERIOSO</t>
+        </is>
+      </c>
+      <c r="D285" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G285" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H285" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I285" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J285" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K285" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L285" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M285" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N285" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="34" customHeight="1">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-004</t>
+        </is>
+      </c>
+      <c r="B286" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C286" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D286" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F286" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G286" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H286" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I286" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J286" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K286" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L286" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M286" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N286" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="34" customHeight="1">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-005</t>
+        </is>
+      </c>
+      <c r="B287" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C287" s="1" t="inlineStr">
+        <is>
+          <t>INASPETTATO INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D287" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E287" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F287" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G287" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H287" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I287" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J287" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K287" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L287" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M287" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N287" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="34" customHeight="1">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-006</t>
+        </is>
+      </c>
+      <c r="B288" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C288" s="1" t="inlineStr">
+        <is>
+          <t>BELLA È INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D288" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E288" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F288" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G288" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H288" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I288" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K288" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L288" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M288" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N288" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="34" customHeight="1">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-007</t>
+        </is>
+      </c>
+      <c r="B289" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C289" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D289" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F289" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G289" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I289" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L289" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M289" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N289" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="34" customHeight="1">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-008</t>
+        </is>
+      </c>
+      <c r="B290" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C290" s="1" t="inlineStr">
+        <is>
+          <t>BELLA INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D290" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E290" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F290" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G290" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H290" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I290" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J290" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K290" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L290" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M290" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N290" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="34" customHeight="1">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-009</t>
+        </is>
+      </c>
+      <c r="B291" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C291" s="1" t="inlineStr">
+        <is>
+          <t>IMMERSIVA, DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D291" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E291" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F291" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G291" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H291" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I291" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J291" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K291" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L291" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M291" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N291" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="34" customHeight="1">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-010</t>
+        </is>
+      </c>
+      <c r="B292" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C292" s="1" t="inlineStr">
+        <is>
+          <t>BELLISSIMA</t>
+        </is>
+      </c>
+      <c r="D292" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E292" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F292" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G292" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I292" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K292" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L292" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M292" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N292" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="34" customHeight="1">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-011</t>
+        </is>
+      </c>
+      <c r="B293" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C293" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D293" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E293" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F293" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G293" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I293" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J293" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K293" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L293" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M293" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N293" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="34" customHeight="1">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-012</t>
+        </is>
+      </c>
+      <c r="B294" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C294" s="1" t="inlineStr">
+        <is>
+          <t>ISTRUTTIVA SIMPATICA</t>
+        </is>
+      </c>
+      <c r="D294" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E294" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F294" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H294" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I294" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J294" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K294" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L294" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M294" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N294" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="34" customHeight="1">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-013</t>
+        </is>
+      </c>
+      <c r="B295" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C295" s="1" t="inlineStr">
+        <is>
+          <t>GREAT EXPERIENCE</t>
+        </is>
+      </c>
+      <c r="D295" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E295" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F295" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G295" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H295" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I295" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J295" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L295" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M295" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N295" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="34" customHeight="1">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-014</t>
+        </is>
+      </c>
+      <c r="B296" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C296" s="1" t="inlineStr">
+        <is>
+          <t>SCHIFOSA DIOCAN</t>
+        </is>
+      </c>
+      <c r="D296" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E296" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F296" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G296" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H296" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I296" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J296" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K296" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L296" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M296" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N296" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="34" customHeight="1">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-015</t>
+        </is>
+      </c>
+      <c r="B297" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C297" s="1" t="inlineStr">
+        <is>
+          <t>BELLA, DIVERTENTE E INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D297" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E297" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F297" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G297" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H297" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I297" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K297" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L297" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M297" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N297" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="34" customHeight="1">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-016</t>
+        </is>
+      </c>
+      <c r="B298" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C298" s="1" t="inlineStr">
+        <is>
+          <t>BELLA E INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D298" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E298" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F298" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G298" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H298" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I298" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K298" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L298" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M298" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N298" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="34" customHeight="1">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-017</t>
+        </is>
+      </c>
+      <c r="B299" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C299" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE, BELLA</t>
+        </is>
+      </c>
+      <c r="D299" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E299" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F299" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G299" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H299" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I299" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J299" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K299" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L299" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M299" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N299" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="34" customHeight="1">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-018</t>
+        </is>
+      </c>
+      <c r="B300" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C300" s="1" t="inlineStr">
+        <is>
+          <t>PIACEVOLE ED INNOVATIVA</t>
+        </is>
+      </c>
+      <c r="D300" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E300" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F300" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G300" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H300" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I300" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L300" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M300" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N300" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="34" customHeight="1">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-019</t>
+        </is>
+      </c>
+      <c r="B301" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C301" s="1" t="inlineStr">
+        <is>
+          <t>BELLISSIMO INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E301" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F301" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H301" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I301" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J301" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L301" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M301" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N301" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="34" customHeight="1">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-020</t>
+        </is>
+      </c>
+      <c r="B302" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C302" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D302" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E302" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F302" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H302" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I302" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K302" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L302" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M302" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N302" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="34" customHeight="1">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-021</t>
+        </is>
+      </c>
+      <c r="B303" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C303" s="1" t="inlineStr">
+        <is>
+          <t>STUPENDO INFORMATIVO</t>
+        </is>
+      </c>
+      <c r="D303" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E303" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F303" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H303" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I303" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J303" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K303" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L303" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M303" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N303" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="34" customHeight="1">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-022</t>
+        </is>
+      </c>
+      <c r="B304" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C304" s="1" t="inlineStr">
+        <is>
+          <t>È STATA ORIGINALE E MOLTO COSTRUTTIVA</t>
+        </is>
+      </c>
+      <c r="D304" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E304" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F304" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H304" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I304" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J304" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L304" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M304" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N304" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="34" customHeight="1">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-023</t>
+        </is>
+      </c>
+      <c r="B305" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C305" s="1" t="inlineStr">
+        <is>
+          <t>BELLO INTERESSANTE DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D305" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E305" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F305" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H305" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I305" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J305" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L305" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M305" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N305" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="34" customHeight="1">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-024</t>
+        </is>
+      </c>
+      <c r="B306" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C306" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE, ILLUSTRATIVA, EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="D306" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E306" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F306" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G306" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H306" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I306" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J306" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L306" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M306" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N306" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="34" customHeight="1">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-025</t>
+        </is>
+      </c>
+      <c r="B307" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C307" s="1" t="inlineStr">
+        <is>
+          <t>COSTRUTTIVA E DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D307" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E307" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F307" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G307" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H307" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I307" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J307" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K307" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L307" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M307" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N307" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="34" customHeight="1">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-026</t>
+        </is>
+      </c>
+      <c r="B308" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C308" s="1" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="D308" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E308" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F308" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G308" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H308" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I308" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J308" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K308" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L308" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M308" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N308" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="34" customHeight="1">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-027</t>
+        </is>
+      </c>
+      <c r="B309" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C309" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D309" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E309" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F309" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G309" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H309" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I309" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K309" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L309" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M309" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N309" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="34" customHeight="1">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-028</t>
+        </is>
+      </c>
+      <c r="B310" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C310" s="1" t="inlineStr">
+        <is>
+          <t>BELLO E INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D310" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E310" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F310" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G310" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H310" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I310" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J310" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K310" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L310" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M310" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N310" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="34" customHeight="1">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-029</t>
+        </is>
+      </c>
+      <c r="B311" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C311" s="1" t="inlineStr">
+        <is>
+          <t>ENTUSIASMANTE INTRIGANTE</t>
+        </is>
+      </c>
+      <c r="D311" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E311" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F311" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G311" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H311" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I311" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K311" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L311" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M311" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N311" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="34" customHeight="1">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-030</t>
+        </is>
+      </c>
+      <c r="B312" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C312" s="1" t="inlineStr">
+        <is>
+          <t>FANTASTICA E DIVERTENTE</t>
+        </is>
+      </c>
+      <c r="D312" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E312" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F312" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G312" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H312" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I312" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J312" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K312" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L312" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M312" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N312" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="34" customHeight="1">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-031</t>
+        </is>
+      </c>
+      <c r="B313" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C313" s="1" t="inlineStr">
+        <is>
+          <t>DIVERTENTE COINVOLGENTE BELLA</t>
+        </is>
+      </c>
+      <c r="D313" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E313" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F313" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H313" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I313" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J313" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L313" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M313" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N313" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="34" customHeight="1">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-032</t>
+        </is>
+      </c>
+      <c r="B314" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C314" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE, COINVOLGENTE</t>
+        </is>
+      </c>
+      <c r="D314" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F314" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G314" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H314" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I314" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J314" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K314" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L314" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M314" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N314" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="34" customHeight="1">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-033</t>
+        </is>
+      </c>
+      <c r="B315" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C315" s="1" t="inlineStr">
+        <is>
+          <t>MOLTO INTERESSANTE E STIMOLANTE!</t>
+        </is>
+      </c>
+      <c r="D315" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E315" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F315" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G315" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H315" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I315" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J315" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K315" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L315" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M315" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N315" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="34" customHeight="1">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-034</t>
+        </is>
+      </c>
+      <c r="B316" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C316" s="1" t="inlineStr">
+        <is>
+          <t>CRAZY, EDUCATIVA E ISPIRATRICE</t>
+        </is>
+      </c>
+      <c r="D316" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E316" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F316" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G316" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H316" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I316" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J316" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K316" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L316" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M316" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N316" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="34" customHeight="1">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-035</t>
+        </is>
+      </c>
+      <c r="B317" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C317" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE 
+DIVERTENTE 
+EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="D317" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E317" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F317" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G317" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H317" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I317" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K317" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L317" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M317" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N317" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="34" customHeight="1">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-036</t>
+        </is>
+      </c>
+      <c r="B318" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C318" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D318" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F318" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G318" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H318" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I318" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J318" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K318" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L318" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M318" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N318" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="34" customHeight="1">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-037</t>
+        </is>
+      </c>
+      <c r="B319" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C319" s="1" t="inlineStr">
+        <is>
+          <t>FANTASTICA ENTUSIASMANTE</t>
+        </is>
+      </c>
+      <c r="D319" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E319" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F319" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G319" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H319" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I319" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J319" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K319" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L319" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M319" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N319" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="34" customHeight="1">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-038</t>
+        </is>
+      </c>
+      <c r="B320" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C320" s="1" t="inlineStr">
+        <is>
+          <t>COINVOLGENTE, EMOZIONANTE</t>
+        </is>
+      </c>
+      <c r="D320" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E320" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F320" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H320" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I320" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K320" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L320" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M320" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N320" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="34" customHeight="1">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-039</t>
+        </is>
+      </c>
+      <c r="B321" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C321" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D321" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F321" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G321" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H321" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I321" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K321" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L321" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M321" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N321" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="34" customHeight="1">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-040</t>
+        </is>
+      </c>
+      <c r="B322" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C322" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="D322" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E322" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F322" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G322" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H322" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I322" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J322" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K322" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L322" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M322" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N322" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="34" customHeight="1">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-041</t>
+        </is>
+      </c>
+      <c r="B323" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C323" s="1" t="inlineStr">
+        <is>
+          <t>PARTICELLA, ESPERIMENTO</t>
+        </is>
+      </c>
+      <c r="D323" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F323" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G323" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H323" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I323" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J323" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K323" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L323" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M323" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N323" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="34" customHeight="1">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-042</t>
+        </is>
+      </c>
+      <c r="B324" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C324" s="1" t="inlineStr">
+        <is>
+          <t>SENSAZIONALE, EMOZIONANTE</t>
+        </is>
+      </c>
+      <c r="D324" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F324" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G324" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H324" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I324" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J324" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K324" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L324" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M324" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N324" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="34" customHeight="1">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-043</t>
+        </is>
+      </c>
+      <c r="B325" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C325" s="1" t="inlineStr">
+        <is>
+          <t>NUOVA, IMMERSIVA, INTELLIGENTE</t>
+        </is>
+      </c>
+      <c r="D325" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E325" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F325" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G325" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H325" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I325" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J325" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K325" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L325" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M325" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N325" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="34" customHeight="1">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-044</t>
+        </is>
+      </c>
+      <c r="B326" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C326" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE,DIVERTENTE,STIMOLANTE</t>
+        </is>
+      </c>
+      <c r="D326" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E326" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F326" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G326" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H326" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I326" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K326" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L326" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M326" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N326" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="34" customHeight="1">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-045</t>
+        </is>
+      </c>
+      <c r="B327" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C327" s="1" t="inlineStr">
+        <is>
+          <t>INDIMENTICABILE</t>
+        </is>
+      </c>
+      <c r="D327" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F327" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G327" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H327" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I327" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J327" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K327" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L327" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M327" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N327" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="34" customHeight="1">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-046</t>
+        </is>
+      </c>
+      <c r="B328" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C328" s="1" t="inlineStr">
+        <is>
+          <t>INTERESSANTE E STIMOLANTE</t>
+        </is>
+      </c>
+      <c r="D328" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E328" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F328" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G328" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H328" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I328" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J328" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K328" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L328" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M328" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N328" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="34" customHeight="1">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-047</t>
+        </is>
+      </c>
+      <c r="B329" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C329" s="1" t="inlineStr">
+        <is>
+          <t>MOLTO INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D329" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E329" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F329" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G329" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H329" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I329" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J329" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K329" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L329" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M329" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N329" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="34" customHeight="1">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-048</t>
+        </is>
+      </c>
+      <c r="B330" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C330" s="1" t="inlineStr">
+        <is>
+          <t>FANTASTICA E INTERESSANTE</t>
+        </is>
+      </c>
+      <c r="D330" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E330" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F330" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G330" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H330" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I330" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K330" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L330" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M330" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N330" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="34" customHeight="1">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-049</t>
+        </is>
+      </c>
+      <c r="B331" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C331" s="1" t="inlineStr">
+        <is>
+          <t>COINVOLGENTE, UNICA, RIPETIBILE</t>
+        </is>
+      </c>
+      <c r="D331" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E331" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F331" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G331" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H331" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I331" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J331" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K331" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L331" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M331" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="N331" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B7:L282">
+  <conditionalFormatting sqref="B7:L331">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>999</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="10">
-    <dataValidation sqref="B7:B282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="B7:B331" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:D282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="D7:D331" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="E7:E282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="E7:E331" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="F7:F282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="F7:F331" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="G7:G282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="G7:G331" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="H7:H282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="H7:H331" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="I7:I282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="I7:I331" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="J7:J282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="J7:J331" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,3,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="K7:K282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="K7:K331" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,2,3,4,5,6,7,999"</formula1>
     </dataValidation>
-    <dataValidation sqref="L7:L282" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
+    <dataValidation sqref="L7:L331" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Codice non valido" error="Usare i codici in legenda; 999 solo per una risposta vuota." type="list">
       <formula1>"0,1,999"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15065,7 +17603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R277"/>
+  <dimension ref="A1:R326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -38110,6 +40648,4100 @@
       </c>
       <c r="R277" s="1" t="inlineStr"/>
     </row>
+    <row r="278" ht="40" customHeight="1">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-001</t>
+        </is>
+      </c>
+      <c r="B278" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C278" s="1" t="inlineStr">
+        <is>
+          <t>Senzazionale</t>
+        </is>
+      </c>
+      <c r="D278" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E278" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F278" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G278" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H278" s="1" t="inlineStr">
+        <is>
+          <t>Spesso</t>
+        </is>
+      </c>
+      <c r="I278" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J278" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K278" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L278" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M278" s="1" t="inlineStr"/>
+      <c r="N278" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=1</t>
+        </is>
+      </c>
+      <c r="O278" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P278" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q278" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R278" s="1" t="inlineStr"/>
+    </row>
+    <row r="279" ht="40" customHeight="1">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-002</t>
+        </is>
+      </c>
+      <c r="B279" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C279" s="1" t="inlineStr">
+        <is>
+          <t>appassionante</t>
+        </is>
+      </c>
+      <c r="D279" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E279" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F279" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G279" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H279" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I279" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J279" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K279" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L279" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M279" s="1" t="inlineStr"/>
+      <c r="N279" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=2</t>
+        </is>
+      </c>
+      <c r="O279" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P279" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q279" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R279" s="1" t="inlineStr"/>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-003</t>
+        </is>
+      </c>
+      <c r="B280" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C280" s="1" t="inlineStr">
+        <is>
+          <t>coinvolgente sensazionale misterioso</t>
+        </is>
+      </c>
+      <c r="D280" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E280" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F280" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G280" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H280" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I280" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J280" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K280" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L280" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M280" s="1" t="inlineStr"/>
+      <c r="N280" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=3</t>
+        </is>
+      </c>
+      <c r="O280" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P280" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q280" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R280" s="1" t="inlineStr"/>
+    </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-004</t>
+        </is>
+      </c>
+      <c r="B281" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C281" s="1" t="inlineStr"/>
+      <c r="D281" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E281" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F281" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G281" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H281" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I281" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J281" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K281" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L281" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M281" s="1" t="inlineStr"/>
+      <c r="N281" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=4</t>
+        </is>
+      </c>
+      <c r="O281" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P281" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q281" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R281" s="1" t="inlineStr"/>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-005</t>
+        </is>
+      </c>
+      <c r="B282" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C282" s="1" t="inlineStr">
+        <is>
+          <t>inaspettato interessante</t>
+        </is>
+      </c>
+      <c r="D282" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E282" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F282" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G282" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H282" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I282" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J282" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K282" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L282" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M282" s="1" t="inlineStr"/>
+      <c r="N282" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=5</t>
+        </is>
+      </c>
+      <c r="O282" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P282" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q282" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R282" s="1" t="inlineStr"/>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-006</t>
+        </is>
+      </c>
+      <c r="B283" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C283" s="1" t="inlineStr">
+        <is>
+          <t>Bella è interessante</t>
+        </is>
+      </c>
+      <c r="D283" s="1" t="inlineStr">
+        <is>
+          <t>No, per niente</t>
+        </is>
+      </c>
+      <c r="E283" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F283" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G283" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H283" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I283" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J283" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K283" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L283" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M283" s="1" t="inlineStr"/>
+      <c r="N283" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=6</t>
+        </is>
+      </c>
+      <c r="O283" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P283" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q283" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R283" s="1" t="inlineStr"/>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-007</t>
+        </is>
+      </c>
+      <c r="B284" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C284" s="1" t="inlineStr">
+        <is>
+          <t>Interessante</t>
+        </is>
+      </c>
+      <c r="D284" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E284" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F284" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G284" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H284" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I284" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J284" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K284" s="1" t="inlineStr">
+        <is>
+          <t>41-60</t>
+        </is>
+      </c>
+      <c r="L284" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M284" s="1" t="inlineStr"/>
+      <c r="N284" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=7</t>
+        </is>
+      </c>
+      <c r="O284" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P284" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q284" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R284" s="1" t="inlineStr"/>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-008</t>
+        </is>
+      </c>
+      <c r="B285" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C285" s="1" t="inlineStr">
+        <is>
+          <t>Bella interessante</t>
+        </is>
+      </c>
+      <c r="D285" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E285" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F285" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G285" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H285" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I285" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J285" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K285" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L285" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M285" s="1" t="inlineStr"/>
+      <c r="N285" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=8</t>
+        </is>
+      </c>
+      <c r="O285" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P285" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q285" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R285" s="1" t="inlineStr"/>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-009</t>
+        </is>
+      </c>
+      <c r="B286" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C286" s="1" t="inlineStr">
+        <is>
+          <t>Immersiva, Divertente</t>
+        </is>
+      </c>
+      <c r="D286" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E286" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F286" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G286" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H286" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I286" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J286" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K286" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L286" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M286" s="1" t="inlineStr"/>
+      <c r="N286" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=9</t>
+        </is>
+      </c>
+      <c r="O286" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P286" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q286" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R286" s="1" t="inlineStr"/>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-010</t>
+        </is>
+      </c>
+      <c r="B287" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C287" s="1" t="inlineStr">
+        <is>
+          <t>bellissima</t>
+        </is>
+      </c>
+      <c r="D287" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E287" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F287" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G287" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H287" s="1" t="inlineStr">
+        <is>
+          <t>Spesso</t>
+        </is>
+      </c>
+      <c r="I287" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J287" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K287" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L287" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M287" s="1" t="inlineStr"/>
+      <c r="N287" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=10</t>
+        </is>
+      </c>
+      <c r="O287" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P287" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q287" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R287" s="1" t="inlineStr"/>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-011</t>
+        </is>
+      </c>
+      <c r="B288" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C288" s="1" t="inlineStr"/>
+      <c r="D288" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E288" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F288" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G288" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H288" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I288" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J288" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K288" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L288" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M288" s="1" t="inlineStr"/>
+      <c r="N288" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=11</t>
+        </is>
+      </c>
+      <c r="O288" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P288" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q288" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R288" s="1" t="inlineStr"/>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-012</t>
+        </is>
+      </c>
+      <c r="B289" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C289" s="1" t="inlineStr">
+        <is>
+          <t>Istruttiva Simpatica</t>
+        </is>
+      </c>
+      <c r="D289" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E289" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F289" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G289" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H289" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I289" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J289" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K289" s="1" t="inlineStr">
+        <is>
+          <t>41-60</t>
+        </is>
+      </c>
+      <c r="L289" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M289" s="1" t="inlineStr"/>
+      <c r="N289" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=12</t>
+        </is>
+      </c>
+      <c r="O289" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P289" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q289" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R289" s="1" t="inlineStr"/>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-013</t>
+        </is>
+      </c>
+      <c r="B290" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C290" s="1" t="inlineStr">
+        <is>
+          <t>great experience</t>
+        </is>
+      </c>
+      <c r="D290" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E290" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F290" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G290" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H290" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I290" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J290" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K290" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L290" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M290" s="1" t="inlineStr"/>
+      <c r="N290" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=13</t>
+        </is>
+      </c>
+      <c r="O290" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P290" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q290" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R290" s="1" t="inlineStr"/>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-014</t>
+        </is>
+      </c>
+      <c r="B291" s="1" t="inlineStr">
+        <is>
+          <t>Non mi è piaciuta molto</t>
+        </is>
+      </c>
+      <c r="C291" s="1" t="inlineStr">
+        <is>
+          <t>schifosa diocan</t>
+        </is>
+      </c>
+      <c r="D291" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E291" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F291" s="1" t="inlineStr">
+        <is>
+          <t>Meno interessato/a</t>
+        </is>
+      </c>
+      <c r="G291" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H291" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I291" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J291" s="1" t="inlineStr">
+        <is>
+          <t>Preferisco non rispondere</t>
+        </is>
+      </c>
+      <c r="K291" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L291" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M291" s="1" t="inlineStr"/>
+      <c r="N291" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=14</t>
+        </is>
+      </c>
+      <c r="O291" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P291" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q291" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R291" s="1" t="inlineStr"/>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-015</t>
+        </is>
+      </c>
+      <c r="B292" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C292" s="1" t="inlineStr">
+        <is>
+          <t>Bella, divertente e interessante</t>
+        </is>
+      </c>
+      <c r="D292" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E292" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F292" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G292" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H292" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I292" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J292" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K292" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L292" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M292" s="1" t="inlineStr"/>
+      <c r="N292" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=15</t>
+        </is>
+      </c>
+      <c r="O292" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P292" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q292" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R292" s="1" t="inlineStr"/>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-016</t>
+        </is>
+      </c>
+      <c r="B293" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C293" s="1" t="inlineStr">
+        <is>
+          <t>bella e interessante</t>
+        </is>
+      </c>
+      <c r="D293" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E293" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F293" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G293" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H293" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I293" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J293" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K293" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L293" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M293" s="1" t="inlineStr"/>
+      <c r="N293" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=16</t>
+        </is>
+      </c>
+      <c r="O293" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P293" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q293" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R293" s="1" t="inlineStr"/>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-017</t>
+        </is>
+      </c>
+      <c r="B294" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C294" s="1" t="inlineStr">
+        <is>
+          <t>Interessante, bella</t>
+        </is>
+      </c>
+      <c r="D294" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E294" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F294" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G294" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H294" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I294" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J294" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K294" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L294" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M294" s="1" t="inlineStr"/>
+      <c r="N294" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=17</t>
+        </is>
+      </c>
+      <c r="O294" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P294" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q294" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R294" s="1" t="inlineStr"/>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-018</t>
+        </is>
+      </c>
+      <c r="B295" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C295" s="1" t="inlineStr">
+        <is>
+          <t>piacevole ed innovativa</t>
+        </is>
+      </c>
+      <c r="D295" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E295" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F295" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G295" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H295" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I295" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J295" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K295" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L295" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M295" s="1" t="inlineStr"/>
+      <c r="N295" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=18</t>
+        </is>
+      </c>
+      <c r="O295" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P295" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q295" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R295" s="1" t="inlineStr"/>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-019</t>
+        </is>
+      </c>
+      <c r="B296" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C296" s="1" t="inlineStr">
+        <is>
+          <t>bellissimo interessante</t>
+        </is>
+      </c>
+      <c r="D296" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E296" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F296" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G296" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H296" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I296" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J296" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K296" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L296" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M296" s="1" t="inlineStr"/>
+      <c r="N296" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=19</t>
+        </is>
+      </c>
+      <c r="O296" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P296" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q296" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R296" s="1" t="inlineStr"/>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-020</t>
+        </is>
+      </c>
+      <c r="B297" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C297" s="1" t="inlineStr"/>
+      <c r="D297" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E297" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F297" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G297" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H297" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I297" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J297" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K297" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L297" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M297" s="1" t="inlineStr"/>
+      <c r="N297" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=20</t>
+        </is>
+      </c>
+      <c r="O297" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P297" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q297" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R297" s="1" t="inlineStr"/>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-021</t>
+        </is>
+      </c>
+      <c r="B298" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C298" s="1" t="inlineStr">
+        <is>
+          <t>stupendo informativo</t>
+        </is>
+      </c>
+      <c r="D298" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E298" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F298" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G298" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H298" s="1" t="inlineStr">
+        <is>
+          <t>Spesso</t>
+        </is>
+      </c>
+      <c r="I298" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J298" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K298" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L298" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M298" s="1" t="inlineStr"/>
+      <c r="N298" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=21</t>
+        </is>
+      </c>
+      <c r="O298" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P298" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q298" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R298" s="1" t="inlineStr"/>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-022</t>
+        </is>
+      </c>
+      <c r="B299" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C299" s="1" t="inlineStr">
+        <is>
+          <t>È stata originale e molto costruttiva</t>
+        </is>
+      </c>
+      <c r="D299" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E299" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F299" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G299" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H299" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I299" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J299" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K299" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L299" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M299" s="1" t="inlineStr"/>
+      <c r="N299" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=22</t>
+        </is>
+      </c>
+      <c r="O299" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P299" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q299" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R299" s="1" t="inlineStr"/>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-023</t>
+        </is>
+      </c>
+      <c r="B300" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C300" s="1" t="inlineStr">
+        <is>
+          <t>Bello interessante divertente</t>
+        </is>
+      </c>
+      <c r="D300" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E300" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F300" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G300" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H300" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I300" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J300" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K300" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L300" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M300" s="1" t="inlineStr"/>
+      <c r="N300" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=23</t>
+        </is>
+      </c>
+      <c r="O300" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P300" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q300" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R300" s="1" t="inlineStr"/>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-024</t>
+        </is>
+      </c>
+      <c r="B301" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C301" s="1" t="inlineStr">
+        <is>
+          <t>interessante, illustrativa, educativa</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E301" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F301" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G301" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H301" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I301" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J301" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K301" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L301" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M301" s="1" t="inlineStr"/>
+      <c r="N301" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=24</t>
+        </is>
+      </c>
+      <c r="O301" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P301" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q301" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R301" s="1" t="inlineStr"/>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-025</t>
+        </is>
+      </c>
+      <c r="B302" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C302" s="1" t="inlineStr">
+        <is>
+          <t>costruttiva e divertente</t>
+        </is>
+      </c>
+      <c r="D302" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E302" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F302" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G302" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H302" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I302" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J302" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K302" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L302" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M302" s="1" t="inlineStr"/>
+      <c r="N302" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=25</t>
+        </is>
+      </c>
+      <c r="O302" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P302" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q302" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R302" s="1" t="inlineStr"/>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-026</t>
+        </is>
+      </c>
+      <c r="B303" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C303" s="1" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="D303" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E303" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F303" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G303" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H303" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I303" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J303" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K303" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L303" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M303" s="1" t="inlineStr"/>
+      <c r="N303" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=26</t>
+        </is>
+      </c>
+      <c r="O303" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P303" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q303" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R303" s="1" t="inlineStr"/>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-027</t>
+        </is>
+      </c>
+      <c r="B304" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C304" s="1" t="inlineStr">
+        <is>
+          <t>Interessante</t>
+        </is>
+      </c>
+      <c r="D304" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E304" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F304" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G304" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H304" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I304" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J304" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K304" s="1" t="inlineStr">
+        <is>
+          <t>11-14</t>
+        </is>
+      </c>
+      <c r="L304" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M304" s="1" t="inlineStr"/>
+      <c r="N304" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=27</t>
+        </is>
+      </c>
+      <c r="O304" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P304" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q304" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R304" s="1" t="inlineStr"/>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-028</t>
+        </is>
+      </c>
+      <c r="B305" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C305" s="1" t="inlineStr">
+        <is>
+          <t>bello e interessante</t>
+        </is>
+      </c>
+      <c r="D305" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E305" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F305" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G305" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H305" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I305" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J305" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K305" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L305" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M305" s="1" t="inlineStr"/>
+      <c r="N305" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=28</t>
+        </is>
+      </c>
+      <c r="O305" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P305" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q305" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R305" s="1" t="inlineStr"/>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-029</t>
+        </is>
+      </c>
+      <c r="B306" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C306" s="1" t="inlineStr">
+        <is>
+          <t>entusiasmante intrigante</t>
+        </is>
+      </c>
+      <c r="D306" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E306" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F306" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G306" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H306" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I306" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J306" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K306" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L306" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M306" s="1" t="inlineStr"/>
+      <c r="N306" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=29</t>
+        </is>
+      </c>
+      <c r="O306" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P306" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q306" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R306" s="1" t="inlineStr"/>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-030</t>
+        </is>
+      </c>
+      <c r="B307" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C307" s="1" t="inlineStr">
+        <is>
+          <t>fantastica e divertente</t>
+        </is>
+      </c>
+      <c r="D307" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E307" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F307" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G307" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H307" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I307" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J307" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K307" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L307" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M307" s="1" t="inlineStr"/>
+      <c r="N307" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=30</t>
+        </is>
+      </c>
+      <c r="O307" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P307" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q307" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R307" s="1" t="inlineStr"/>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-031</t>
+        </is>
+      </c>
+      <c r="B308" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C308" s="1" t="inlineStr">
+        <is>
+          <t>divertente coinvolgente bella</t>
+        </is>
+      </c>
+      <c r="D308" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E308" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F308" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G308" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H308" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I308" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J308" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K308" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L308" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M308" s="1" t="inlineStr"/>
+      <c r="N308" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=31</t>
+        </is>
+      </c>
+      <c r="O308" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P308" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q308" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R308" s="1" t="inlineStr"/>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-032</t>
+        </is>
+      </c>
+      <c r="B309" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C309" s="1" t="inlineStr">
+        <is>
+          <t>Interessante, coinvolgente</t>
+        </is>
+      </c>
+      <c r="D309" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E309" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F309" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G309" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H309" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I309" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J309" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K309" s="1" t="inlineStr">
+        <is>
+          <t>19-25</t>
+        </is>
+      </c>
+      <c r="L309" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M309" s="1" t="inlineStr"/>
+      <c r="N309" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=32</t>
+        </is>
+      </c>
+      <c r="O309" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P309" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q309" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R309" s="1" t="inlineStr"/>
+    </row>
+    <row r="310" ht="40" customHeight="1">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-033</t>
+        </is>
+      </c>
+      <c r="B310" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C310" s="1" t="inlineStr">
+        <is>
+          <t>Molto interessante e stimolante!</t>
+        </is>
+      </c>
+      <c r="D310" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E310" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F310" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G310" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H310" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I310" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J310" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K310" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L310" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M310" s="1" t="inlineStr"/>
+      <c r="N310" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=33</t>
+        </is>
+      </c>
+      <c r="O310" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P310" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q310" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R310" s="1" t="inlineStr"/>
+    </row>
+    <row r="311" ht="40" customHeight="1">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-034</t>
+        </is>
+      </c>
+      <c r="B311" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C311" s="1" t="inlineStr">
+        <is>
+          <t>Crazy, educativa e ispiratrice</t>
+        </is>
+      </c>
+      <c r="D311" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E311" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F311" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G311" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H311" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I311" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J311" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K311" s="1" t="inlineStr">
+        <is>
+          <t>19-25</t>
+        </is>
+      </c>
+      <c r="L311" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M311" s="1" t="inlineStr"/>
+      <c r="N311" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=34</t>
+        </is>
+      </c>
+      <c r="O311" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P311" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q311" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R311" s="1" t="inlineStr"/>
+    </row>
+    <row r="312" ht="40" customHeight="1">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-035</t>
+        </is>
+      </c>
+      <c r="B312" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C312" s="1" t="inlineStr">
+        <is>
+          <t>interessante 
+divertente 
+educativa</t>
+        </is>
+      </c>
+      <c r="D312" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E312" s="1" t="inlineStr">
+        <is>
+          <t>Curioso/a come prima</t>
+        </is>
+      </c>
+      <c r="F312" s="1" t="inlineStr">
+        <is>
+          <t>Interessato/a come prima</t>
+        </is>
+      </c>
+      <c r="G312" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H312" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I312" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J312" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K312" s="1" t="inlineStr">
+        <is>
+          <t>19-25</t>
+        </is>
+      </c>
+      <c r="L312" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M312" s="1" t="inlineStr"/>
+      <c r="N312" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=35</t>
+        </is>
+      </c>
+      <c r="O312" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P312" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q312" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R312" s="1" t="inlineStr"/>
+    </row>
+    <row r="313" ht="40" customHeight="1">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-036</t>
+        </is>
+      </c>
+      <c r="B313" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C313" s="1" t="inlineStr"/>
+      <c r="D313" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E313" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F313" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G313" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H313" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I313" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J313" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K313" s="1" t="inlineStr">
+        <is>
+          <t>26-40</t>
+        </is>
+      </c>
+      <c r="L313" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M313" s="1" t="inlineStr"/>
+      <c r="N313" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=36</t>
+        </is>
+      </c>
+      <c r="O313" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P313" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q313" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R313" s="1" t="inlineStr"/>
+    </row>
+    <row r="314" ht="40" customHeight="1">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-037</t>
+        </is>
+      </c>
+      <c r="B314" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C314" s="1" t="inlineStr">
+        <is>
+          <t>Fantastica entusiasmante</t>
+        </is>
+      </c>
+      <c r="D314" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E314" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F314" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G314" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H314" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I314" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J314" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K314" s="1" t="inlineStr">
+        <is>
+          <t>41-60</t>
+        </is>
+      </c>
+      <c r="L314" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M314" s="1" t="inlineStr"/>
+      <c r="N314" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=37</t>
+        </is>
+      </c>
+      <c r="O314" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P314" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q314" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R314" s="1" t="inlineStr"/>
+    </row>
+    <row r="315" ht="40" customHeight="1">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-038</t>
+        </is>
+      </c>
+      <c r="B315" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C315" s="1" t="inlineStr">
+        <is>
+          <t>Coinvolgente, emozionante</t>
+        </is>
+      </c>
+      <c r="D315" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E315" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F315" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G315" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H315" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I315" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J315" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K315" s="1" t="inlineStr">
+        <is>
+          <t>41-60</t>
+        </is>
+      </c>
+      <c r="L315" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M315" s="1" t="inlineStr"/>
+      <c r="N315" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=38</t>
+        </is>
+      </c>
+      <c r="O315" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P315" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q315" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R315" s="1" t="inlineStr"/>
+    </row>
+    <row r="316" ht="40" customHeight="1">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-039</t>
+        </is>
+      </c>
+      <c r="B316" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C316" s="1" t="inlineStr"/>
+      <c r="D316" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E316" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F316" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G316" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H316" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I316" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J316" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K316" s="1" t="inlineStr">
+        <is>
+          <t>19-25</t>
+        </is>
+      </c>
+      <c r="L316" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M316" s="1" t="inlineStr"/>
+      <c r="N316" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=39</t>
+        </is>
+      </c>
+      <c r="O316" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P316" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q316" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R316" s="1" t="inlineStr"/>
+    </row>
+    <row r="317" ht="40" customHeight="1">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-040</t>
+        </is>
+      </c>
+      <c r="B317" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C317" s="1" t="inlineStr"/>
+      <c r="D317" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E317" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F317" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G317" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H317" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I317" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J317" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K317" s="1" t="inlineStr">
+        <is>
+          <t>Più di 60</t>
+        </is>
+      </c>
+      <c r="L317" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M317" s="1" t="inlineStr"/>
+      <c r="N317" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=40</t>
+        </is>
+      </c>
+      <c r="O317" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P317" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q317" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R317" s="1" t="inlineStr"/>
+    </row>
+    <row r="318" ht="40" customHeight="1">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-041</t>
+        </is>
+      </c>
+      <c r="B318" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C318" s="1" t="inlineStr">
+        <is>
+          <t>Particella, esperimento</t>
+        </is>
+      </c>
+      <c r="D318" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E318" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F318" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G318" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H318" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I318" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J318" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K318" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L318" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M318" s="1" t="inlineStr"/>
+      <c r="N318" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=41</t>
+        </is>
+      </c>
+      <c r="O318" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P318" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q318" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R318" s="1" t="inlineStr"/>
+    </row>
+    <row r="319" ht="40" customHeight="1">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-042</t>
+        </is>
+      </c>
+      <c r="B319" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C319" s="1" t="inlineStr">
+        <is>
+          <t>sensazionale, emozionante</t>
+        </is>
+      </c>
+      <c r="D319" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E319" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F319" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G319" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H319" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I319" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J319" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K319" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L319" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M319" s="1" t="inlineStr"/>
+      <c r="N319" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=42</t>
+        </is>
+      </c>
+      <c r="O319" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P319" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q319" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R319" s="1" t="inlineStr"/>
+    </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-043</t>
+        </is>
+      </c>
+      <c r="B320" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C320" s="1" t="inlineStr">
+        <is>
+          <t>Nuova, immersiva, intelligente</t>
+        </is>
+      </c>
+      <c r="D320" s="1" t="inlineStr">
+        <is>
+          <t>Sì, un po’</t>
+        </is>
+      </c>
+      <c r="E320" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F320" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G320" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H320" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I320" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J320" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K320" s="1" t="inlineStr">
+        <is>
+          <t>41-60</t>
+        </is>
+      </c>
+      <c r="L320" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M320" s="1" t="inlineStr"/>
+      <c r="N320" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=43</t>
+        </is>
+      </c>
+      <c r="O320" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P320" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q320" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R320" s="1" t="inlineStr"/>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-044</t>
+        </is>
+      </c>
+      <c r="B321" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C321" s="1" t="inlineStr">
+        <is>
+          <t>Interessante,divertente,stimolante</t>
+        </is>
+      </c>
+      <c r="D321" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E321" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F321" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G321" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H321" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I321" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J321" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K321" s="1" t="inlineStr">
+        <is>
+          <t>41-60</t>
+        </is>
+      </c>
+      <c r="L321" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M321" s="1" t="inlineStr"/>
+      <c r="N321" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=44</t>
+        </is>
+      </c>
+      <c r="O321" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P321" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q321" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R321" s="1" t="inlineStr"/>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-045</t>
+        </is>
+      </c>
+      <c r="B322" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta</t>
+        </is>
+      </c>
+      <c r="C322" s="1" t="inlineStr">
+        <is>
+          <t>indimenticabile</t>
+        </is>
+      </c>
+      <c r="D322" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E322" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F322" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G322" s="1" t="inlineStr">
+        <is>
+          <t>In parte</t>
+        </is>
+      </c>
+      <c r="H322" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I322" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J322" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K322" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L322" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M322" s="1" t="inlineStr"/>
+      <c r="N322" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=45</t>
+        </is>
+      </c>
+      <c r="O322" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P322" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q322" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R322" s="1" t="inlineStr"/>
+    </row>
+    <row r="323" ht="40" customHeight="1">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-046</t>
+        </is>
+      </c>
+      <c r="B323" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C323" s="1" t="inlineStr">
+        <is>
+          <t>Interessante e stimolante</t>
+        </is>
+      </c>
+      <c r="D323" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E323" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F323" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G323" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H323" s="1" t="inlineStr">
+        <is>
+          <t>A volte</t>
+        </is>
+      </c>
+      <c r="I323" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="J323" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K323" s="1" t="inlineStr">
+        <is>
+          <t>15-18</t>
+        </is>
+      </c>
+      <c r="L323" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M323" s="1" t="inlineStr"/>
+      <c r="N323" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=46</t>
+        </is>
+      </c>
+      <c r="O323" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P323" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q323" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R323" s="1" t="inlineStr"/>
+    </row>
+    <row r="324" ht="40" customHeight="1">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-047</t>
+        </is>
+      </c>
+      <c r="B324" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C324" s="1" t="inlineStr">
+        <is>
+          <t>Molto interessante</t>
+        </is>
+      </c>
+      <c r="D324" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E324" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F324" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G324" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H324" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I324" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J324" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K324" s="1" t="inlineStr">
+        <is>
+          <t>Più di 60</t>
+        </is>
+      </c>
+      <c r="L324" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M324" s="1" t="inlineStr"/>
+      <c r="N324" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=47</t>
+        </is>
+      </c>
+      <c r="O324" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P324" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q324" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R324" s="1" t="inlineStr"/>
+    </row>
+    <row r="325" ht="40" customHeight="1">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-048</t>
+        </is>
+      </c>
+      <c r="B325" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C325" s="1" t="inlineStr">
+        <is>
+          <t>Fantastica e interessante</t>
+        </is>
+      </c>
+      <c r="D325" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E325" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F325" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G325" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H325" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I325" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J325" s="1" t="inlineStr">
+        <is>
+          <t>Femminile</t>
+        </is>
+      </c>
+      <c r="K325" s="1" t="inlineStr">
+        <is>
+          <t>41-60</t>
+        </is>
+      </c>
+      <c r="L325" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M325" s="1" t="inlineStr"/>
+      <c r="N325" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=48</t>
+        </is>
+      </c>
+      <c r="O325" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P325" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q325" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R325" s="1" t="inlineStr"/>
+    </row>
+    <row r="326" ht="40" customHeight="1">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>ROMA-AVZ-ONLINE-ERN2026-049</t>
+        </is>
+      </c>
+      <c r="B326" s="1" t="inlineStr">
+        <is>
+          <t>Mi è piaciuta tantissimo</t>
+        </is>
+      </c>
+      <c r="C326" s="1" t="inlineStr">
+        <is>
+          <t>Coinvolgente, unica, ripetibile</t>
+        </is>
+      </c>
+      <c r="D326" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="E326" s="1" t="inlineStr">
+        <is>
+          <t>Più curioso/a</t>
+        </is>
+      </c>
+      <c r="F326" s="1" t="inlineStr">
+        <is>
+          <t>Più interessato/a</t>
+        </is>
+      </c>
+      <c r="G326" s="1" t="inlineStr">
+        <is>
+          <t>Sì, molto</t>
+        </is>
+      </c>
+      <c r="H326" s="1" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="I326" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J326" s="1" t="inlineStr">
+        <is>
+          <t>Maschile</t>
+        </is>
+      </c>
+      <c r="K326" s="1" t="inlineStr">
+        <is>
+          <t>Meno di 11</t>
+        </is>
+      </c>
+      <c r="L326" s="1" t="inlineStr">
+        <is>
+          <t>Sì</t>
+        </is>
+      </c>
+      <c r="M326" s="1" t="inlineStr"/>
+      <c r="N326" s="1" t="inlineStr">
+        <is>
+          <t>roma_avezzano_online_originale.tsv#risposta=49</t>
+        </is>
+      </c>
+      <c r="O326" s="1" t="inlineStr">
+        <is>
+          <t>Avezzano</t>
+        </is>
+      </c>
+      <c r="P326" s="1" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="Q326" s="1" t="inlineStr">
+        <is>
+          <t>Confermata</t>
+        </is>
+      </c>
+      <c r="R326" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
